--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AFBAC3-2C64-41F1-A8D3-C998905552FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC74706-E66E-4754-9E89-A9B0B8FD8FFC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
-    <sheet name="07-01-2026" sheetId="57" r:id="rId2"/>
+    <sheet name="07-02-2026" sheetId="57" r:id="rId2"/>
+    <sheet name="07-03-2026" sheetId="58" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'07-01-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'07-03-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="72">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -252,7 +254,7 @@
     <t xml:space="preserve">DATE: </t>
   </si>
   <si>
-    <t>DATE: 07/01/2026</t>
+    <t>DATE: 07/02/2026</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1241,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1525,6 +1527,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1941,21 +1946,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="104" t="s">
+      <c r="I1" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
-      <c r="O1" s="104"/>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="104"/>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="104"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1967,17 +1972,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="107"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -1997,13 +2002,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="108" t="s">
+      <c r="T4" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="110" t="s">
+      <c r="U4" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="97" t="s">
+      <c r="V4" s="98" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2043,10 +2048,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="99" t="s">
+      <c r="J5" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="100"/>
+      <c r="K5" s="101"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2054,9 +2059,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="109"/>
-      <c r="U5" s="111"/>
-      <c r="V5" s="98"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="99"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4587,17 +4592,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="101" t="s">
+      <c r="C62" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="102"/>
-      <c r="E62" s="102"/>
-      <c r="F62" s="102"/>
-      <c r="G62" s="102"/>
-      <c r="H62" s="102"/>
-      <c r="I62" s="102"/>
-      <c r="J62" s="102"/>
-      <c r="K62" s="103"/>
+      <c r="D62" s="103"/>
+      <c r="E62" s="103"/>
+      <c r="F62" s="103"/>
+      <c r="G62" s="103"/>
+      <c r="H62" s="103"/>
+      <c r="I62" s="103"/>
+      <c r="J62" s="103"/>
+      <c r="K62" s="104"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4906,21 +4911,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="104" t="s">
+      <c r="I1" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
-      <c r="O1" s="104"/>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="104"/>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="104"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4932,17 +4937,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="107"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4962,13 +4967,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="108" t="s">
+      <c r="T4" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="114" t="s">
+      <c r="U4" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="97" t="s">
+      <c r="V4" s="98" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5008,10 +5013,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="112" t="s">
+      <c r="J5" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="113"/>
+      <c r="K5" s="114"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5019,9 +5024,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="109"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="98"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="99"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -5098,34 +5103,44 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>993</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>41.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -5160,7 +5175,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>52+53</f>
+        <v>105</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -5170,11 +5188,17 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -5183,11 +5207,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2616</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -5222,7 +5246,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>151</f>
+        <v>151</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -5234,9 +5261,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -5245,11 +5276,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>3696</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -5284,7 +5315,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>118</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -5294,7 +5327,9 @@
       <c r="J10" s="71"/>
       <c r="K10" s="72"/>
       <c r="L10" s="55"/>
-      <c r="M10" s="73"/>
+      <c r="M10" s="73">
+        <v>2</v>
+      </c>
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
@@ -5307,11 +5342,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -5346,7 +5381,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -5354,7 +5391,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -5365,15 +5404,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.083333333333334</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -5406,7 +5445,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>288+68+1277+1440+864</f>
+        <v>3937</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -5416,24 +5458,34 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="M12" s="63">
+        <v>8</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>1</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="Q12" s="66">
+        <v>16</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>95112</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3963</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -5475,12 +5527,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -5494,15 +5550,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -5536,7 +5592,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -5559,11 +5617,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -5724,7 +5782,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -5738,15 +5799,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -5840,12 +5901,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -5859,15 +5925,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -5901,7 +5967,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -5924,11 +5992,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -5967,7 +6035,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -5981,15 +6052,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -6029,7 +6100,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -6042,15 +6115,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -6098,7 +6171,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -6112,15 +6188,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -6163,12 +6239,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -6182,15 +6263,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -6224,34 +6305,45 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>63+47</f>
+        <v>110</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>3</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2785</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>116.04166666666667</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -6313,7 +6405,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -6336,11 +6430,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -6360,7 +6454,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <f>126+11</f>
+        <v>137</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -6370,7 +6467,9 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
       <c r="N28" s="74"/>
       <c r="O28" s="70"/>
       <c r="P28" s="71"/>
@@ -6383,11 +6482,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3336</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -6407,13 +6506,17 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>22</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
@@ -6421,20 +6524,22 @@
       <c r="N29" s="74"/>
       <c r="O29" s="70"/>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -6445,7 +6550,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -6459,7 +6566,9 @@
       <c r="N30" s="74"/>
       <c r="O30" s="70"/>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>2</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -6468,11 +6577,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -6597,34 +6706,49 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>11+144</f>
+        <v>155</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3854</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>160.58333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6711,34 +6835,51 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>1728+2160</f>
+        <v>3888</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>4</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>47</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>1</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>55</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>23959</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3993.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -6826,7 +6967,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>32+63+63</f>
+        <v>158</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -6834,26 +6978,34 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>3956</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>164.83333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6864,7 +7016,9 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <v>34</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -6876,9 +7030,13 @@
       <c r="L41" s="85"/>
       <c r="M41" s="86"/>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>2</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>19</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -6887,11 +7045,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6931,34 +7089,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>24948+14472+10260</f>
+        <v>49680</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>2</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>6*6</f>
+        <v>36</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>324</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>110</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>453</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>303833</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>50638.833333333336</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -7036,7 +7213,9 @@
       <c r="B46" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="70"/>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
       <c r="D46" s="70"/>
       <c r="E46" s="70"/>
       <c r="F46" s="70"/>
@@ -7059,11 +7238,11 @@
       </c>
       <c r="U46" s="75">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V46" s="75">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -7074,34 +7253,51 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>756+64+324+98+540+432+432+106</f>
+        <v>2752</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
       <c r="M47" s="63"/>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16597</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2766.1666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -7117,7 +7313,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -7131,15 +7329,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -7226,7 +7424,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -7249,11 +7449,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -7302,7 +7502,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -7325,11 +7527,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -7455,7 +7657,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>61365</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -7469,56 +7671,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1190</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1735</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>467395</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>62576.416666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7526,17 +7728,3147 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="101" t="s">
+      <c r="C60" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="102"/>
-      <c r="E60" s="102"/>
-      <c r="F60" s="102"/>
-      <c r="G60" s="102"/>
-      <c r="H60" s="102"/>
-      <c r="I60" s="102"/>
-      <c r="J60" s="102"/>
-      <c r="K60" s="103"/>
+      <c r="D60" s="103"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="103"/>
+      <c r="G60" s="103"/>
+      <c r="H60" s="103"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="103"/>
+      <c r="K60" s="104"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{927A4B96-3533-428D-BFE2-67602408452B}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="105" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="115" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="113" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="114"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="97"/>
+      <c r="Q5" s="97"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="99"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="97"/>
+      <c r="Q6" s="97"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56">
+        <v>1</v>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>993</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>41.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>52+53</f>
+        <v>105</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2616</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>109</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>151</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3696</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>154</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>118</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>2832</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>118</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>10.083333333333334</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>288+40+1224+53+864+1440</f>
+        <v>3909</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>8</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>14</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>18</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>94788</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3949.5</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>47+63</f>
+        <v>110</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>2</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2761</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>115.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <v>126</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>10</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>3288</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>137</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>22</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>557</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>23.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>2</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>11+144</f>
+        <v>155</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3830</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>159.58333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2160+1620+15</f>
+        <v>3795</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>4</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>22</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>40</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>56</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>23491</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3915.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>50+63</f>
+        <v>113</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>2852</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>118.83333333333333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>16</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>2</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>31</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>588</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>24948+13500+10260</f>
+        <v>48708</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>7*6+2</f>
+        <v>44</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>366</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>434</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>505</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>437</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>300515</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>50085.833333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>96</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>756+64+324+98+540+432+432+106</f>
+        <v>2752</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16597</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2766.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>60182</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1188</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>49</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>418</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>507</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>636</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1729</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>461941</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>61872.916666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="102" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="103"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="103"/>
+      <c r="G60" s="103"/>
+      <c r="H60" s="103"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="103"/>
+      <c r="K60" s="104"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,18 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC74706-E66E-4754-9E89-A9B0B8FD8FFC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B918FED4-091B-44DC-A961-E8CD9BB79E09}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
     <sheet name="07-02-2026" sheetId="57" r:id="rId2"/>
     <sheet name="07-03-2026" sheetId="58" r:id="rId3"/>
+    <sheet name="07-06-2026" sheetId="60" r:id="rId4"/>
+    <sheet name="07-07-2026" sheetId="59" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'07-03-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'07-06-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'07-07-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="74">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -255,6 +259,12 @@
   </si>
   <si>
     <t>DATE: 07/02/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/06/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/07/2026</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1251,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1527,6 +1537,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1946,21 +1959,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1972,17 +1985,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2002,13 +2015,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="111" t="s">
+      <c r="U4" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2048,10 +2061,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="100" t="s">
+      <c r="J5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="101"/>
+      <c r="K5" s="102"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2059,9 +2072,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4592,17 +4605,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="102" t="s">
+      <c r="C62" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="103"/>
-      <c r="E62" s="103"/>
-      <c r="F62" s="103"/>
-      <c r="G62" s="103"/>
-      <c r="H62" s="103"/>
-      <c r="I62" s="103"/>
-      <c r="J62" s="103"/>
-      <c r="K62" s="104"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="104"/>
+      <c r="K62" s="105"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4911,21 +4924,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4937,17 +4950,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4967,13 +4980,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5013,10 +5026,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="113" t="s">
+      <c r="J5" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="114"/>
+      <c r="K5" s="115"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5024,9 +5037,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7728,17 +7741,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8047,21 +8060,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8073,17 +8086,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8103,13 +8116,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8149,10 +8162,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="113" t="s">
+      <c r="J5" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="114"/>
+      <c r="K5" s="115"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8160,9 +8173,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10858,17 +10871,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11135,4 +11148,6068 @@
     <brk id="24" max="80" man="1"/>
   </colBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BAC8289-9E3D-410B-AF16-4E6DE22FEF92}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="106" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="116" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="114" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="115"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="98"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="100"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="98"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>969</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>40.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>51+53</f>
+        <v>104</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2592</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>108</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>150</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>1</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3696</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>154</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>117</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73">
+        <v>1</v>
+      </c>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>2832</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>118</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>10.083333333333334</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>288+15+1224+53+1440+864</f>
+        <v>3884</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>7</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>94116</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3921.5</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>1*24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>40+63</f>
+        <v>103</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>6</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2689</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>112.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>63+56</f>
+        <v>119</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>4</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>3024</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>126</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>22</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>533</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>22.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>11+144</f>
+        <v>155</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3830</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>159.58333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2160+1512</f>
+        <v>3672</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>14</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>25</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>110</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>22939</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3823.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>48+63</f>
+        <v>111</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>2780</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>115.83333333333333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>1</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>12</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>24948+12366+10260</f>
+        <v>47574</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>7</v>
+      </c>
+      <c r="I43" s="65">
+        <f>8*6+2</f>
+        <v>50</v>
+      </c>
+      <c r="J43" s="66">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="K43" s="67"/>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>340</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>436</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>470</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>443</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>293363</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>48893.833333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>96</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>756+64+324+98+540+432+432+106</f>
+        <v>2752</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16597</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2766.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70">
+        <v>9</v>
+      </c>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>216</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>58881</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1194</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>81</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>393</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>36</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>371</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>490</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>619</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1735</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>452485</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>60491.916666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="103" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1037665-E275-40D3-9163-C22CCDE28F1A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="106" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="116" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="114" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="115"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="98"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="100"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="98"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63"/>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="103" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
 </file>
--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B918FED4-091B-44DC-A961-E8CD9BB79E09}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F668F3DB-6A6F-494B-B7D2-79F823C38BA9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -14258,13 +14258,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -14507,34 +14507,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>40.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -14569,7 +14577,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>51+53</f>
+        <v>104</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -14579,11 +14590,15 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
       <c r="O8" s="65"/>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -14592,11 +14607,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -14631,7 +14646,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>150</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -14643,9 +14660,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -14654,11 +14675,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>3672</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -14693,7 +14714,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>117</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -14716,11 +14739,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2808</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -14755,7 +14778,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -14763,7 +14788,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -14774,15 +14801,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.083333333333334</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -14815,7 +14842,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>216+52+1224+53+864+1440</f>
+        <v>3849</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -14825,11 +14855,17 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>12</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="O12" s="65">
+        <v>15</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
+      <c r="Q12" s="66">
+        <v>16</v>
+      </c>
       <c r="R12" s="67"/>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
@@ -14838,11 +14874,11 @@
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>93408</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3892</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -14884,12 +14920,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -14903,15 +14943,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -14945,7 +14985,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -14968,11 +15010,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -15133,7 +15175,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -15147,15 +15192,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -15249,12 +15294,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -15268,15 +15318,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -15310,7 +15360,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -15333,11 +15385,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -15376,7 +15428,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -15390,15 +15445,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -15438,7 +15493,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -15451,15 +15508,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -15507,7 +15564,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -15521,15 +15581,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -15572,12 +15632,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -15591,15 +15656,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -15633,34 +15698,45 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>38+63</f>
+        <v>101</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2521</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>105.04166666666667</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -15722,7 +15798,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -15745,11 +15823,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -15769,7 +15847,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <f>56+63</f>
+        <v>119</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -15781,9 +15862,13 @@
       <c r="L28" s="55"/>
       <c r="M28" s="73"/>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
       <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
+      <c r="Q28" s="71">
+        <v>4</v>
+      </c>
       <c r="R28" s="72"/>
       <c r="S28" s="55"/>
       <c r="T28" s="58">
@@ -15792,11 +15877,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -15816,13 +15901,17 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>22</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
@@ -15835,15 +15924,15 @@
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>533</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>22.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -15854,7 +15943,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -15868,7 +15959,9 @@
       <c r="N30" s="74"/>
       <c r="O30" s="70"/>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -15877,11 +15970,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -16006,34 +16099,49 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>11+144</f>
+        <v>155</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3830</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>159.58333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16120,34 +16228,51 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>2160+1404</f>
+        <v>3564</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>11</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>108</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>90</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>22651</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3775.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -16235,7 +16360,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>48+63</f>
+        <v>111</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -16243,26 +16371,32 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
       <c r="M40" s="63"/>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>2780</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>115.83333333333333</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16287,7 +16421,9 @@
       <c r="N41" s="87"/>
       <c r="O41" s="82"/>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>1</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -16296,11 +16432,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16340,34 +16476,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>24948+11492+10260</f>
+        <v>46700</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
       <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>8*6+2</f>
+        <v>50</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>329</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>398</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>428</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>287573</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>47928.833333333336</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16445,7 +16598,9 @@
       <c r="B46" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="70"/>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
       <c r="D46" s="70"/>
       <c r="E46" s="70"/>
       <c r="F46" s="70"/>
@@ -16468,11 +16623,11 @@
       </c>
       <c r="U46" s="75">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V46" s="75">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16483,34 +16638,51 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>756+64+324+98+540+432+432+106</f>
+        <v>2752</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
       <c r="M47" s="63"/>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16597</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2766.1666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -16526,7 +16698,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -16540,15 +16714,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -16635,7 +16809,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -16658,11 +16834,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -16711,7 +16887,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -16734,11 +16912,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -16864,7 +17042,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>57862</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -16878,23 +17056,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -16902,32 +17080,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1723</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>445459</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>59439.416666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -17197,13 +17375,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F668F3DB-6A6F-494B-B7D2-79F823C38BA9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356C700C-54F6-4DC5-9231-275E1E67B272}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -18,12 +18,14 @@
     <sheet name="07-03-2026" sheetId="58" r:id="rId3"/>
     <sheet name="07-06-2026" sheetId="60" r:id="rId4"/>
     <sheet name="07-07-2026" sheetId="59" r:id="rId5"/>
+    <sheet name="07-08-2026 " sheetId="61" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'07-03-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'07-06-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-07-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'07-08-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="76">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -265,6 +267,12 @@
   </si>
   <si>
     <t>DATE: 07/07/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/08/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/03/2026</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1259,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1537,6 +1545,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1959,21 +1970,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1985,17 +1996,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2015,13 +2026,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="112" t="s">
+      <c r="U4" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2061,10 +2072,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="101" t="s">
+      <c r="J5" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="103"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2072,9 +2083,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4605,17 +4616,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="103" t="s">
+      <c r="C62" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
-      <c r="H62" s="104"/>
-      <c r="I62" s="104"/>
-      <c r="J62" s="104"/>
-      <c r="K62" s="105"/>
+      <c r="D62" s="105"/>
+      <c r="E62" s="105"/>
+      <c r="F62" s="105"/>
+      <c r="G62" s="105"/>
+      <c r="H62" s="105"/>
+      <c r="I62" s="105"/>
+      <c r="J62" s="105"/>
+      <c r="K62" s="106"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4924,21 +4935,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4950,17 +4961,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4980,13 +4991,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5026,10 +5037,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="116"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5037,9 +5048,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7741,17 +7752,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8060,25 +8071,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -8086,17 +8097,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8116,13 +8127,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8162,10 +8173,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="116"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8173,9 +8184,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10871,17 +10882,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11190,21 +11201,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11216,17 +11227,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11246,13 +11257,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11292,10 +11303,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="116"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11303,9 +11314,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13996,17 +14007,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14315,21 +14326,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14341,17 +14352,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14371,13 +14382,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14417,10 +14428,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="116"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14428,9 +14439,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17113,17 +17124,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17390,4 +17401,3129 @@
     <brk id="24" max="80" man="1"/>
   </colBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFB43EB-A9D9-4100-9758-308E0CB02E8D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="117" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="115" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="116"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="101"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="99"/>
+      <c r="Q6" s="99"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>969</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>40.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>51+53</f>
+        <v>104</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2568</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>107</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>136</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>15</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3672</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>153</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>98</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70">
+        <v>2</v>
+      </c>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71">
+        <v>17</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>2808</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>117</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>10.083333333333334</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>216+17+1224+53+1440+864</f>
+        <v>3814</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>10</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>13</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>22</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>92616</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3859</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>38+63</f>
+        <v>101</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2521</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>105.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>63+52</f>
+        <v>115</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>4</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>2928</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>122</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>20</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>2</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>533</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>22.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>7+144</f>
+        <v>151</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>3</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3782</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>157.58333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2160+1296+34</f>
+        <v>3490</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>20</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>38</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>55</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>21631</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3605.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>48+63</f>
+        <v>111</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>2780</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>115.83333333333333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>24948+10476+10260</f>
+        <v>45684</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>5</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>13*6+1</f>
+        <v>79</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>329</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>406</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>471</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>477</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>281817</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>46969.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70">
+        <v>3</v>
+      </c>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70">
+        <v>1</v>
+      </c>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>96</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>756+64+324+98+540+432+432+106</f>
+        <v>2752</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16597</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2766.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>56693</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1192</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>85</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>365</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>479</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>597</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1757</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>437735</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>58270.083333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="104" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
 </file>
--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356C700C-54F6-4DC5-9231-275E1E67B272}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5400D2D-8151-4004-8D34-9A3B1587DF82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="07-06-2026" sheetId="60" r:id="rId4"/>
     <sheet name="07-07-2026" sheetId="59" r:id="rId5"/>
     <sheet name="07-08-2026 " sheetId="61" r:id="rId6"/>
+    <sheet name="07-09-2026" sheetId="62" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
@@ -26,6 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'07-06-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-07-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'07-08-2026 '!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07-09-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="76">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1259,7 +1261,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1545,6 +1547,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1970,21 +1975,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1996,17 +2001,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2026,13 +2031,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="113" t="s">
+      <c r="U4" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2072,10 +2077,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="104"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2083,9 +2088,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="115"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4616,17 +4621,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="104" t="s">
+      <c r="C62" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="105"/>
-      <c r="E62" s="105"/>
-      <c r="F62" s="105"/>
-      <c r="G62" s="105"/>
-      <c r="H62" s="105"/>
-      <c r="I62" s="105"/>
-      <c r="J62" s="105"/>
-      <c r="K62" s="106"/>
+      <c r="D62" s="106"/>
+      <c r="E62" s="106"/>
+      <c r="F62" s="106"/>
+      <c r="G62" s="106"/>
+      <c r="H62" s="106"/>
+      <c r="I62" s="106"/>
+      <c r="J62" s="106"/>
+      <c r="K62" s="107"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4935,21 +4940,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4961,17 +4966,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4991,13 +4996,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5037,10 +5042,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5048,9 +5053,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7752,17 +7757,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8071,21 +8076,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8097,17 +8102,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8127,13 +8132,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8173,10 +8178,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8184,9 +8189,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10882,17 +10887,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11201,21 +11206,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11227,17 +11232,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11257,13 +11262,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11303,10 +11308,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11314,9 +11319,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14007,17 +14012,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14326,21 +14331,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14352,17 +14357,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14382,13 +14387,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14428,10 +14433,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14439,9 +14444,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17124,17 +17129,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17443,21 +17448,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17469,17 +17474,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17499,13 +17504,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17545,10 +17550,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17556,9 +17561,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20249,17 +20254,3144 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B904888E-B760-4BA9-BF9D-453ECF1FAC1E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="118" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="116" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="117"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>969</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>40.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>51+53</f>
+        <v>104</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2568</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>107</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>135</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>1</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3312</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>138</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>99</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73">
+        <v>1</v>
+      </c>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>2400</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>10.083333333333334</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>144+59+1224+53+1440+864</f>
+        <v>3784</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>19</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>15</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>92124</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3838.5</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>63+37</f>
+        <v>100</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>2</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2521</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>105.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>63+50</f>
+        <v>113</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>4</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>2904</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>121</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>18</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>509</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>21.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>2+144</f>
+        <v>146</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>3</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3638</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>151.58333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2160+1188+80</f>
+        <v>3428</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>20</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>20</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>34</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>21025</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3504.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>3+63</f>
+        <v>66</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>1676</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>69.833333333333329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>24948+9612+10260</f>
+        <v>44820</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>5</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>14*6+1</f>
+        <v>85</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>363</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>368</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>421</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>483</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>276315</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>46052.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>96</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>61+756+324+98+540+432+432+106</f>
+        <v>2749</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>3</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>9</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16597</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2766.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>55680</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1192</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>91</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>415</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>419</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>494</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1775</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>429071</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>57145.583333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="105" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5400D2D-8151-4004-8D34-9A3B1587DF82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76DFA21-6D83-4E37-85F6-B15482AF37A8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="07-07-2026" sheetId="59" r:id="rId5"/>
     <sheet name="07-08-2026 " sheetId="61" r:id="rId6"/>
     <sheet name="07-09-2026" sheetId="62" r:id="rId7"/>
+    <sheet name="07-10-2026" sheetId="63" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
@@ -28,6 +29,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-07-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'07-08-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'07-09-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'07-10-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="77">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -275,6 +277,9 @@
   </si>
   <si>
     <t>DATE: 07/03/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/09/2026</t>
   </si>
 </sst>
 </file>
@@ -1261,7 +1266,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1547,6 +1552,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1975,21 +1983,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2001,17 +2009,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2031,13 +2039,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="114" t="s">
+      <c r="U4" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2077,10 +2085,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="103" t="s">
+      <c r="J5" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="104"/>
+      <c r="K5" s="105"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2088,9 +2096,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4621,17 +4629,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="105" t="s">
+      <c r="C62" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="106"/>
-      <c r="E62" s="106"/>
-      <c r="F62" s="106"/>
-      <c r="G62" s="106"/>
-      <c r="H62" s="106"/>
-      <c r="I62" s="106"/>
-      <c r="J62" s="106"/>
-      <c r="K62" s="107"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="107"/>
+      <c r="H62" s="107"/>
+      <c r="I62" s="107"/>
+      <c r="J62" s="107"/>
+      <c r="K62" s="108"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4940,21 +4948,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4966,17 +4974,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4996,13 +5004,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5042,10 +5050,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5053,9 +5061,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7757,17 +7765,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8076,21 +8084,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8102,17 +8110,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8132,13 +8140,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8178,10 +8186,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8189,9 +8197,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10887,17 +10895,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11206,21 +11214,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11232,17 +11240,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11262,13 +11270,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11308,10 +11316,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11319,9 +11327,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14012,17 +14020,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14331,21 +14339,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14357,17 +14365,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14387,13 +14395,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14433,10 +14441,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14444,9 +14452,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17129,17 +17137,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17448,21 +17456,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17474,17 +17482,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17504,13 +17512,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17550,10 +17558,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17561,9 +17569,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20254,17 +20262,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20573,25 +20581,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -20599,17 +20607,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20629,13 +20637,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20675,10 +20683,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20686,9 +20694,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23381,17 +23389,3134 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94C8284-9421-41FC-87BD-1886EFE3B765}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="109" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="119" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="117" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="118"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="101"/>
+      <c r="Q6" s="101"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>969</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>40.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>51+53</f>
+        <v>104</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2568</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>107</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>135</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3240</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>135</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>99</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>2376</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>99</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>10.083333333333334</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>144+59+1224+53+1440+864</f>
+        <v>3784</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>9</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>5</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>16</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>91560</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3815</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>37+63</f>
+        <v>100</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2497</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>104.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>63+47</f>
+        <v>110</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>3</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>2736</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>114</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>18</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>509</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>21.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>2+144</f>
+        <v>146</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>3</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3614</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>150.58333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2160+1188+51</f>
+        <v>3399</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>10</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>54</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>20791</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3465.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>3+63</f>
+        <v>66</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>1676</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>69.833333333333329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>24948+9504+10260</f>
+        <v>44712</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>5</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>14*6+1</f>
+        <v>85</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>7</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>76</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>396</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>483</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>271629</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>45271.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>96</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>61+756+324+98+540+432+432+106</f>
+        <v>2749</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>8</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16573</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2762.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>55540</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1192</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>91</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>21</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>102</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>484</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1787</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>423251</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>56285.083333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76DFA21-6D83-4E37-85F6-B15482AF37A8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D0B0FC-4471-45F1-AE5A-7A02FC12D9FE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="07-08-2026 " sheetId="61" r:id="rId6"/>
     <sheet name="07-09-2026" sheetId="62" r:id="rId7"/>
     <sheet name="07-10-2026" sheetId="63" r:id="rId8"/>
+    <sheet name="07-13-2026" sheetId="64" r:id="rId9"/>
+    <sheet name="07-13-2026 (2)" sheetId="65" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
@@ -30,6 +32,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'07-08-2026 '!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'07-09-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'07-10-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'07-13-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'07-13-2026 (2)'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="78">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -280,6 +284,9 @@
   </si>
   <si>
     <t>DATE: 07/09/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/13/2026</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1273,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1552,6 +1559,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1983,21 +1993,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2009,17 +2019,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2039,13 +2049,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2085,10 +2095,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="104" t="s">
+      <c r="J5" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="105"/>
+      <c r="K5" s="106"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2096,9 +2106,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4629,17 +4639,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="106" t="s">
+      <c r="C62" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="107"/>
-      <c r="E62" s="107"/>
-      <c r="F62" s="107"/>
-      <c r="G62" s="107"/>
-      <c r="H62" s="107"/>
-      <c r="I62" s="107"/>
-      <c r="J62" s="107"/>
-      <c r="K62" s="108"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="108"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108"/>
+      <c r="H62" s="108"/>
+      <c r="I62" s="108"/>
+      <c r="J62" s="108"/>
+      <c r="K62" s="109"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4902,6 +4912,2945 @@
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="14" scale="53" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA55B008-E772-4B69-B187-24A0943C3075}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="114" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="120" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="118" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="119"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63"/>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="24" max="80" man="1"/>
   </colBreaks>
@@ -4948,21 +7897,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4974,17 +7923,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5004,13 +7953,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5050,10 +7999,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5061,9 +8010,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7765,17 +10714,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8084,21 +11033,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8110,17 +11059,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8140,13 +11089,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8186,10 +11135,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8197,9 +11146,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10895,17 +13844,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11214,21 +14163,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11240,17 +14189,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11270,13 +14219,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11316,10 +14265,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11327,9 +14276,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14020,17 +16969,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14339,21 +17288,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14365,17 +17314,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14395,13 +17344,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14441,10 +17390,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14452,9 +17401,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17137,17 +20086,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17456,21 +20405,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17482,17 +20431,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17512,13 +20461,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17558,10 +20507,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17569,9 +20518,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20262,17 +23211,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20581,21 +23530,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20607,17 +23556,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20637,13 +23586,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20683,10 +23632,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20694,9 +23643,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23389,17 +26338,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23708,21 +26657,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23734,17 +26683,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23764,13 +26713,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23810,10 +26759,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23821,9 +26770,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26506,17 +29455,3152 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0716723-9446-491D-A4E7-CC9D2ABCB74D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="114" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="120" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="118" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="119"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>969</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>40.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>50+53</f>
+        <v>103</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2544</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>106</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <v>132</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>1</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>1</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>3240</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>135</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>95</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73">
+        <v>2</v>
+      </c>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70">
+        <v>1</v>
+      </c>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71">
+        <v>1</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>2376</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>99</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>10.083333333333334</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>144+41+1224+53+1440+864</f>
+        <v>3766</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>9</v>
+      </c>
+      <c r="N12" s="64">
+        <v>12</v>
+      </c>
+      <c r="O12" s="65">
+        <v>13</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66">
+        <v>22</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>91452</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3810.5</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>96</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>24*1+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>36+63</f>
+        <v>99</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>3</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>2497</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>104.04166666666667</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>63+45</f>
+        <v>108</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>3</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>2712</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>113</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>17</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>509</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>21.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>72+64</f>
+        <v>136</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>10</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3590</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>149.58333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2160+1080+66</f>
+        <v>3306</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>10</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>42</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>59</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>20515</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3419.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>63+3</f>
+        <v>66</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>1628</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>67.833333333333329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>24948+8424+10260</f>
+        <v>43632</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>3</v>
+      </c>
+      <c r="I43" s="65">
+        <v>7</v>
+      </c>
+      <c r="J43" s="66">
+        <f>14*6+3</f>
+        <v>87</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>331</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>400</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>552</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>483</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>269973</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>44995.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>96</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>61+756+324+98+540+432+432+106</f>
+        <v>2749</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>8</v>
+      </c>
+      <c r="P47" s="66">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>3</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16573</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2762.1666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>216</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>54327</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1190</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>33</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>99</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>422</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>367</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>472</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>650</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1775</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>421091</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>55953.583333333328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC0F4FF-4069-4FEC-939D-9400BB2EA1D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF50DE8-2A63-413B-B0D7-2B923A06EA80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="9" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="10" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -8300,34 +8300,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53">
+        <v>6</v>
+      </c>
       <c r="K7" s="54"/>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>40.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -8362,7 +8370,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>47+53</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -8372,11 +8383,17 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -8385,11 +8402,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2472</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -8424,7 +8441,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>120</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -8434,11 +8453,15 @@
       <c r="J9" s="71"/>
       <c r="K9" s="72"/>
       <c r="L9" s="55"/>
-      <c r="M9" s="73"/>
+      <c r="M9" s="73">
+        <v>1</v>
+      </c>
       <c r="N9" s="74"/>
       <c r="O9" s="70"/>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>8</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -8447,11 +8470,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>3096</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -8486,7 +8509,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>94</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -8496,7 +8521,9 @@
       <c r="J10" s="71"/>
       <c r="K10" s="72"/>
       <c r="L10" s="55"/>
-      <c r="M10" s="73"/>
+      <c r="M10" s="73">
+        <v>1</v>
+      </c>
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
@@ -8509,11 +8536,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2280</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -8548,14 +8575,18 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
-      <c r="J11" s="71"/>
+      <c r="J11" s="71">
+        <v>2</v>
+      </c>
       <c r="K11" s="72"/>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
@@ -8567,15 +8598,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.083333333333334</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -8608,7 +8639,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>72+41+1224+53+1440+864</f>
+        <v>3694</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -8618,24 +8652,32 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>13</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="O12" s="65">
+        <v>11</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="Q12" s="66">
+        <v>15</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>89604</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3733.5</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -8677,12 +8719,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -8696,15 +8742,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -8738,7 +8784,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -8761,11 +8809,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -8926,7 +8974,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -8940,15 +8991,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -9042,12 +9093,18 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <f>2</f>
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>1*24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -9061,15 +9118,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -9103,7 +9160,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -9126,11 +9185,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -9169,7 +9228,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -9183,15 +9245,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -9231,7 +9293,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -9244,15 +9308,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -9300,7 +9364,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -9314,15 +9381,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -9365,12 +9432,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -9384,15 +9456,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -9426,34 +9498,45 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>31+61</f>
+        <v>92</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2305</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96.041666666666671</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -9515,7 +9598,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -9538,11 +9623,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -9562,7 +9647,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <f>63+38</f>
+        <v>101</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -9572,11 +9660,17 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
       <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
+      <c r="Q28" s="71">
+        <v>2</v>
+      </c>
       <c r="R28" s="72"/>
       <c r="S28" s="55"/>
       <c r="T28" s="58">
@@ -9585,11 +9679,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -9609,34 +9703,40 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>15</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
       <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
       <c r="N29" s="74"/>
       <c r="O29" s="70"/>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>17.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -9661,7 +9761,9 @@
       <c r="N30" s="74"/>
       <c r="O30" s="70"/>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -9670,11 +9772,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -9799,34 +9901,49 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>72+62</f>
+        <v>134</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
       <c r="I34" s="70"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="J34" s="71">
+        <v>1</v>
+      </c>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3350</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>139.58333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -9913,34 +10030,51 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>2160+58+756</f>
+        <v>2974</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>28</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>36</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>90</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>18781</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3130.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -10028,7 +10162,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>5+3</f>
+        <v>8</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -10036,26 +10173,34 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>12.833333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10133,34 +10278,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>24948+5904+10260</f>
+        <v>41112</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>2</v>
+      </c>
+      <c r="I43" s="65">
+        <v>8</v>
+      </c>
+      <c r="J43" s="66">
+        <f>18*6+3</f>
+        <v>111</v>
+      </c>
+      <c r="K43" s="67">
+        <f>64*6+2</f>
+        <v>386</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>289</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>367</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>466</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>253911</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>42318.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -10238,7 +10402,9 @@
       <c r="B46" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="70"/>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
       <c r="D46" s="70"/>
       <c r="E46" s="70"/>
       <c r="F46" s="70"/>
@@ -10261,11 +10427,11 @@
       </c>
       <c r="U46" s="75">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V46" s="75">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10276,34 +10442,51 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>8+756+324+98+540+432+432+106</f>
+        <v>2696</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>20</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>21</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>20</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16551</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2758.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -10319,7 +10502,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -10333,15 +10518,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -10428,7 +10613,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -10451,11 +10638,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -10504,7 +10691,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -10527,11 +10716,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -10657,7 +10846,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>51256</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -10671,23 +10860,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1189</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -10695,32 +10884,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1795</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>399073</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>52808.916666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -10990,13 +11179,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -13929,13 +14118,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -16868,13 +17057,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF50DE8-2A63-413B-B0D7-2B923A06EA80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782B6986-1ABD-417A-B61D-98294D258962}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="10" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="12" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -26,6 +26,8 @@
     <sheet name="07-15-2026" sheetId="66" r:id="rId11"/>
     <sheet name="07-16-2026" sheetId="67" r:id="rId12"/>
     <sheet name="07-17-2026" sheetId="68" r:id="rId13"/>
+    <sheet name="07-18-2026" sheetId="69" r:id="rId14"/>
+    <sheet name="07-19-2026" sheetId="70" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
@@ -40,6 +42,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'07-15-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'07-16-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'07-17-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'07-18-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'07-19-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -58,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="84">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -305,6 +309,12 @@
   </si>
   <si>
     <t>DATE: 07/17/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/18/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/19/2026</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1301,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1577,6 +1587,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2014,21 +2027,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2040,17 +2053,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2070,13 +2083,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2116,10 +2129,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="106" t="s">
+      <c r="J5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="107"/>
+      <c r="K5" s="108"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2127,9 +2140,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4660,17 +4673,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="108" t="s">
+      <c r="C62" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="109"/>
-      <c r="E62" s="109"/>
-      <c r="F62" s="109"/>
-      <c r="G62" s="109"/>
-      <c r="H62" s="109"/>
-      <c r="I62" s="109"/>
-      <c r="J62" s="109"/>
-      <c r="K62" s="110"/>
+      <c r="D62" s="110"/>
+      <c r="E62" s="110"/>
+      <c r="F62" s="110"/>
+      <c r="G62" s="110"/>
+      <c r="H62" s="110"/>
+      <c r="I62" s="110"/>
+      <c r="J62" s="110"/>
+      <c r="K62" s="111"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4979,21 +4992,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5005,17 +5018,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5035,13 +5048,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5081,10 +5094,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5092,9 +5105,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7789,17 +7802,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8108,21 +8121,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8134,17 +8147,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8164,13 +8177,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8210,10 +8223,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8221,9 +8234,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10917,17 +10930,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11236,21 +11249,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11262,17 +11275,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11292,13 +11305,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11338,10 +11351,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11349,9 +11362,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13856,17 +13869,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14175,21 +14188,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14201,17 +14214,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14231,13 +14244,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14277,10 +14290,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14288,9 +14301,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14367,34 +14380,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>40.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -14429,7 +14450,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>45+53</f>
+        <v>98</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -14439,11 +14463,17 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>2</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -14452,11 +14482,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -14491,7 +14521,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>117</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -14501,11 +14533,15 @@
       <c r="J9" s="71"/>
       <c r="K9" s="72"/>
       <c r="L9" s="55"/>
-      <c r="M9" s="73"/>
+      <c r="M9" s="73">
+        <v>1</v>
+      </c>
       <c r="N9" s="74"/>
       <c r="O9" s="70"/>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -14514,11 +14550,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -14553,7 +14589,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>90</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -14563,11 +14601,15 @@
       <c r="J10" s="71"/>
       <c r="K10" s="72"/>
       <c r="L10" s="55"/>
-      <c r="M10" s="73"/>
+      <c r="M10" s="73">
+        <v>1</v>
+      </c>
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>3</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -14576,11 +14618,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2256</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -14615,7 +14657,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -14623,7 +14667,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -14634,15 +14680,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.083333333333334</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -14675,7 +14721,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>72+31+1224+53+1440+864</f>
+        <v>3684</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -14685,11 +14734,17 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>10</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="O12" s="65">
+        <v>11</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
+      <c r="Q12" s="66">
+        <v>11</v>
+      </c>
       <c r="R12" s="67"/>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
@@ -14698,11 +14753,11 @@
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>89184</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -14744,12 +14799,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -14763,15 +14822,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -14805,7 +14864,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -14828,11 +14889,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -14993,7 +15054,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -15007,15 +15071,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -15109,12 +15173,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -15128,15 +15197,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -15170,7 +15239,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -15193,11 +15264,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -15236,7 +15307,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -15250,15 +15324,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -15298,7 +15372,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -15311,15 +15387,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -15367,7 +15443,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>24*37+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -15381,15 +15460,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -15432,12 +15511,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -15451,15 +15535,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -15493,34 +15577,43 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>30+61</f>
+        <v>91</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>2</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
       <c r="Q25" s="71"/>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2257</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>94.041666666666671</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -15540,7 +15633,10 @@
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
       <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
+      <c r="H26" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I26" s="70"/>
       <c r="J26" s="71"/>
       <c r="K26" s="72"/>
@@ -15554,15 +15650,15 @@
       <c r="S26" s="55"/>
       <c r="T26" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U26" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V26" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -15582,7 +15678,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -15605,11 +15703,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -15629,7 +15727,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <f>63+35</f>
+        <v>98</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -15639,9 +15740,13 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
       <c r="P28" s="71"/>
       <c r="Q28" s="71"/>
       <c r="R28" s="72"/>
@@ -15652,11 +15757,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2472</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -15676,34 +15781,42 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>13</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
+      <c r="H29" s="70">
+        <v>5</v>
+      </c>
       <c r="I29" s="70"/>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
-      <c r="M29" s="73"/>
+      <c r="M29" s="73">
+        <v>2</v>
+      </c>
       <c r="N29" s="74"/>
       <c r="O29" s="70"/>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -15714,7 +15827,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>1</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -15737,11 +15852,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -15795,7 +15910,10 @@
       <c r="E32" s="70"/>
       <c r="F32" s="70"/>
       <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
+      <c r="H32" s="70">
+        <f>5*24</f>
+        <v>120</v>
+      </c>
       <c r="I32" s="70"/>
       <c r="J32" s="71"/>
       <c r="K32" s="72"/>
@@ -15809,15 +15927,15 @@
       <c r="S32" s="55"/>
       <c r="T32" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U32" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V32" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
@@ -15833,7 +15951,10 @@
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
       <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
+      <c r="H33" s="70">
+        <f>5*24</f>
+        <v>120</v>
+      </c>
       <c r="I33" s="70"/>
       <c r="J33" s="71"/>
       <c r="K33" s="72"/>
@@ -15847,15 +15968,15 @@
       <c r="S33" s="55"/>
       <c r="T33" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -15866,34 +15987,49 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>72+62</f>
+        <v>134</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
       <c r="I34" s="70"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="J34" s="71">
+        <v>1</v>
+      </c>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3350</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>139.58333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -15980,34 +16116,51 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>24+48+756+2160</f>
+        <v>2988</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>10</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>23</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>16</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>18235</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3039.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -16024,7 +16177,10 @@
       <c r="E38" s="70"/>
       <c r="F38" s="70"/>
       <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
+      <c r="H38" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I38" s="70"/>
       <c r="J38" s="71"/>
       <c r="K38" s="72"/>
@@ -16038,15 +16194,15 @@
       <c r="S38" s="55"/>
       <c r="T38" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U38" s="75">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V38" s="75">
         <f>U38/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -16095,34 +16251,48 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>3+4</f>
+        <v>7</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
       <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
+      <c r="H40" s="59">
+        <f>63*24</f>
+        <v>1512</v>
+      </c>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1532</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>1820</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>75.833333333333329</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16138,7 +16308,10 @@
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
       <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
+      <c r="H41" s="82">
+        <f>384*12</f>
+        <v>4608</v>
+      </c>
       <c r="I41" s="82"/>
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
@@ -16152,15 +16325,15 @@
       <c r="S41" s="85"/>
       <c r="T41" s="88">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4608</v>
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>4608</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>384</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16200,34 +16373,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>18+24192+5400+10260+19+1296</f>
+        <v>41185</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>1</v>
+      </c>
+      <c r="I43" s="65">
+        <v>8</v>
+      </c>
+      <c r="J43" s="66">
+        <f>18*6+4</f>
+        <v>112</v>
+      </c>
+      <c r="K43" s="67">
+        <f>46*6+2</f>
+        <v>278</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>563</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>402</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>648</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>257187</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>42864.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16272,7 +16464,10 @@
       <c r="E45" s="70"/>
       <c r="F45" s="70"/>
       <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
+      <c r="H45" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I45" s="70"/>
       <c r="J45" s="71"/>
       <c r="K45" s="72"/>
@@ -16286,15 +16481,15 @@
       <c r="S45" s="55"/>
       <c r="T45" s="75">
         <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -16305,7 +16500,9 @@
       <c r="B46" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="70"/>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
       <c r="D46" s="70"/>
       <c r="E46" s="70"/>
       <c r="F46" s="70"/>
@@ -16328,11 +16525,11 @@
       </c>
       <c r="U46" s="75">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V46" s="75">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16343,34 +16540,53 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>106+648+324+98+540+432+432+106</f>
+        <v>2686</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>17</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="O47" s="65">
+        <v>18</v>
+      </c>
+      <c r="P47" s="66">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>20</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16457</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2742.8333333333335</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -16386,7 +16602,10 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <f>24</f>
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -16400,15 +16619,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -16495,7 +16714,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -16518,11 +16739,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -16571,7 +16792,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -16594,11 +16817,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -16724,7 +16947,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>51308</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -16738,23 +16961,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7769</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -16762,32 +16985,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>706</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>8253</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>407433</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>53678.75</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -16795,17 +17018,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17064,6 +17287,5884 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F25570-961A-4F51-8ABE-D25E61E306DD}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="116" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="121"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63"/>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D468F1-D5DD-475C-93E9-25D40F9C597E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="116" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="121"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63"/>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -17114,21 +23215,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17140,17 +23241,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17170,13 +23271,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17216,10 +23317,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17227,9 +23328,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -19931,17 +26032,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20250,21 +26351,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20276,17 +26377,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20306,13 +26407,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20352,10 +26453,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20363,9 +26464,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23061,17 +29162,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23380,21 +29481,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23406,17 +29507,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23436,13 +29537,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23482,10 +29583,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23493,9 +29594,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26186,17 +32287,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26505,21 +32606,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26531,17 +32632,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26561,13 +32662,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26607,10 +32708,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26618,9 +32719,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29303,17 +35404,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -29622,21 +35723,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -29648,17 +35749,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -29678,13 +35779,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -29724,10 +35825,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -29735,9 +35836,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32428,17 +38529,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -32747,21 +38848,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -32773,17 +38874,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -32803,13 +38904,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -32849,10 +38950,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -32860,9 +38961,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35555,17 +41656,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -35874,21 +41975,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -35900,17 +42001,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -35930,13 +42031,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -35976,10 +42077,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -35987,9 +42088,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -38672,17 +44773,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -38991,21 +45092,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39017,17 +45118,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39047,13 +45148,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39093,10 +45194,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39104,9 +45205,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -41807,17 +47908,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782B6986-1ABD-417A-B61D-98294D258962}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC0C791-7D51-41CC-A8A8-FF97DDCE4820}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="12" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
@@ -24,10 +24,10 @@
     <sheet name="07-13-2026" sheetId="64" r:id="rId9"/>
     <sheet name="07-14-2026" sheetId="65" r:id="rId10"/>
     <sheet name="07-15-2026" sheetId="66" r:id="rId11"/>
-    <sheet name="07-16-2026" sheetId="67" r:id="rId12"/>
-    <sheet name="07-17-2026" sheetId="68" r:id="rId13"/>
-    <sheet name="07-18-2026" sheetId="69" r:id="rId14"/>
-    <sheet name="07-19-2026" sheetId="70" r:id="rId15"/>
+    <sheet name="07-17-2026" sheetId="68" r:id="rId12"/>
+    <sheet name="07-21-2026" sheetId="67" r:id="rId13"/>
+    <sheet name="07-22-2026" sheetId="69" r:id="rId14"/>
+    <sheet name="07-23-2026" sheetId="70" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
@@ -40,10 +40,10 @@
     <definedName name="_xlnm.Print_Area" localSheetId="8">'07-13-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'07-14-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'07-15-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'07-16-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'07-17-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'07-18-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'07-19-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'07-17-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'07-21-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'07-22-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'07-23-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -305,16 +305,16 @@
     <t>DATE: 07/14/2026</t>
   </si>
   <si>
-    <t>DATE: 07/16/2026</t>
-  </si>
-  <si>
     <t>DATE: 07/17/2026</t>
   </si>
   <si>
-    <t>DATE: 07/18/2026</t>
+    <t>DATE: 07/21/2026</t>
   </si>
   <si>
-    <t>DATE: 07/19/2026</t>
+    <t>DATE: 07/22/2026</t>
+  </si>
+  <si>
+    <t>DATE: 07/23/2026</t>
   </si>
 </sst>
 </file>
@@ -11210,7 +11210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5684B93-2964-4511-A9EF-980363CCF3A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE4AC886-5881-4B77-84A7-F4FAAC6EEA5D}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11441,34 +11441,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>39</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>40.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -11503,7 +11511,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>45+53</f>
+        <v>98</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -11513,11 +11524,17 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>2</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -11526,11 +11543,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -11565,7 +11582,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>117</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -11575,11 +11594,15 @@
       <c r="J9" s="71"/>
       <c r="K9" s="72"/>
       <c r="L9" s="55"/>
-      <c r="M9" s="73"/>
+      <c r="M9" s="73">
+        <v>1</v>
+      </c>
       <c r="N9" s="74"/>
       <c r="O9" s="70"/>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -11588,11 +11611,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -11627,7 +11650,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>90</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -11637,11 +11662,15 @@
       <c r="J10" s="71"/>
       <c r="K10" s="72"/>
       <c r="L10" s="55"/>
-      <c r="M10" s="73"/>
+      <c r="M10" s="73">
+        <v>1</v>
+      </c>
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>3</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -11650,11 +11679,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2256</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -11689,7 +11718,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>10</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -11697,7 +11728,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -11708,15 +11741,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.083333333333334</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -11749,7 +11782,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>72+31+1224+53+1440+864</f>
+        <v>3684</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -11759,11 +11795,17 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>10</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="O12" s="65">
+        <v>11</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
+      <c r="Q12" s="66">
+        <v>11</v>
+      </c>
       <c r="R12" s="67"/>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
@@ -11772,11 +11814,11 @@
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>89184</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -11818,12 +11860,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -11837,15 +11883,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -11879,7 +11925,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>4</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -11902,11 +11950,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -12067,7 +12115,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -12081,15 +12132,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -12183,12 +12234,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -12202,15 +12258,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -12244,7 +12300,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -12267,11 +12325,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -12310,7 +12368,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -12324,15 +12385,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -12372,7 +12433,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -12385,15 +12448,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -12441,7 +12504,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>24*37+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -12455,15 +12521,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -12506,12 +12572,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>5</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -12525,15 +12596,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -12567,34 +12638,43 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>30+61</f>
+        <v>91</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>2</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
       <c r="Q25" s="71"/>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2257</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>94.041666666666671</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -12614,7 +12694,10 @@
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
       <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
+      <c r="H26" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I26" s="70"/>
       <c r="J26" s="71"/>
       <c r="K26" s="72"/>
@@ -12628,15 +12711,15 @@
       <c r="S26" s="55"/>
       <c r="T26" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U26" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V26" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -12656,7 +12739,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -12679,11 +12764,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -12703,7 +12788,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <f>63+35</f>
+        <v>98</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -12713,9 +12801,13 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
       <c r="P28" s="71"/>
       <c r="Q28" s="71"/>
       <c r="R28" s="72"/>
@@ -12726,11 +12818,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2472</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -12750,34 +12842,42 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>13</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
+      <c r="H29" s="70">
+        <v>5</v>
+      </c>
       <c r="I29" s="70"/>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
-      <c r="M29" s="73"/>
+      <c r="M29" s="73">
+        <v>2</v>
+      </c>
       <c r="N29" s="74"/>
       <c r="O29" s="70"/>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -12788,7 +12888,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>1</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -12811,11 +12913,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -12869,7 +12971,10 @@
       <c r="E32" s="70"/>
       <c r="F32" s="70"/>
       <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
+      <c r="H32" s="70">
+        <f>5*24</f>
+        <v>120</v>
+      </c>
       <c r="I32" s="70"/>
       <c r="J32" s="71"/>
       <c r="K32" s="72"/>
@@ -12883,15 +12988,15 @@
       <c r="S32" s="55"/>
       <c r="T32" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U32" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V32" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
@@ -12907,7 +13012,10 @@
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
       <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
+      <c r="H33" s="70">
+        <f>5*24</f>
+        <v>120</v>
+      </c>
       <c r="I33" s="70"/>
       <c r="J33" s="71"/>
       <c r="K33" s="72"/>
@@ -12921,15 +13029,15 @@
       <c r="S33" s="55"/>
       <c r="T33" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -12940,34 +13048,49 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>72+62</f>
+        <v>134</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
       <c r="I34" s="70"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="J34" s="71">
+        <v>1</v>
+      </c>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="O34" s="70">
+        <v>1</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3350</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>139.58333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13054,34 +13177,51 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>24+48+756+2160</f>
+        <v>2988</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>10</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>23</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>16</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>18235</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3039.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -13098,7 +13238,10 @@
       <c r="E38" s="70"/>
       <c r="F38" s="70"/>
       <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
+      <c r="H38" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I38" s="70"/>
       <c r="J38" s="71"/>
       <c r="K38" s="72"/>
@@ -13112,15 +13255,15 @@
       <c r="S38" s="55"/>
       <c r="T38" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U38" s="75">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V38" s="75">
         <f>U38/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -13169,34 +13312,48 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>3+4</f>
+        <v>7</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
       <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
+      <c r="H40" s="59">
+        <f>63*24</f>
+        <v>1512</v>
+      </c>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1532</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>1820</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>75.833333333333329</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13212,7 +13369,10 @@
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
       <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
+      <c r="H41" s="82">
+        <f>384*12</f>
+        <v>4608</v>
+      </c>
       <c r="I41" s="82"/>
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
@@ -13226,15 +13386,15 @@
       <c r="S41" s="85"/>
       <c r="T41" s="88">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4608</v>
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>4608</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>384</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13274,34 +13434,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>18+24192+5400+10260+19+1296</f>
+        <v>41185</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>1</v>
+      </c>
+      <c r="I43" s="65">
+        <v>8</v>
+      </c>
+      <c r="J43" s="66">
+        <f>18*6+4</f>
+        <v>112</v>
+      </c>
+      <c r="K43" s="67">
+        <f>46*6+2</f>
+        <v>278</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>563</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>402</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>648</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>257187</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>42864.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13346,7 +13525,10 @@
       <c r="E45" s="70"/>
       <c r="F45" s="70"/>
       <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
+      <c r="H45" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I45" s="70"/>
       <c r="J45" s="71"/>
       <c r="K45" s="72"/>
@@ -13360,15 +13542,15 @@
       <c r="S45" s="55"/>
       <c r="T45" s="75">
         <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -13379,7 +13561,9 @@
       <c r="B46" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="70"/>
+      <c r="C46" s="70">
+        <v>4</v>
+      </c>
       <c r="D46" s="70"/>
       <c r="E46" s="70"/>
       <c r="F46" s="70"/>
@@ -13402,11 +13586,11 @@
       </c>
       <c r="U46" s="75">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V46" s="75">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13417,34 +13601,53 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>106+648+324+98+540+432+432+106</f>
+        <v>2686</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>17</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="O47" s="65">
+        <v>18</v>
+      </c>
+      <c r="P47" s="66">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>20</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16457</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2742.8333333333335</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -13460,7 +13663,10 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <f>24</f>
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -13474,15 +13680,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -13569,7 +13775,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -13592,11 +13800,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -13645,7 +13853,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>9</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -13668,11 +13878,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -13798,7 +14008,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>51308</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -13812,23 +14022,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7769</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -13836,32 +14046,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>706</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>8253</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>407433</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>53678.75</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -14149,7 +14359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE4AC886-5881-4B77-84A7-F4FAAC6EEA5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5684B93-2964-4511-A9EF-980363CCF3A3}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -14159,8 +14369,7 @@
     <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
     <col min="3" max="6" width="10" style="9" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
     <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
@@ -14522,7 +14731,8 @@
         <v>33</v>
       </c>
       <c r="C9" s="70">
-        <v>117</v>
+        <f>102</f>
+        <v>102</v>
       </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
@@ -14539,9 +14749,7 @@
       <c r="N9" s="74"/>
       <c r="O9" s="70"/>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71">
-        <v>2</v>
-      </c>
+      <c r="Q9" s="71"/>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -14550,11 +14758,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>2880</v>
+        <v>2472</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -14590,7 +14798,7 @@
         <v>36</v>
       </c>
       <c r="C10" s="70">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
@@ -14607,9 +14815,7 @@
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71">
-        <v>3</v>
-      </c>
+      <c r="Q10" s="71"/>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -14618,11 +14824,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>2256</v>
+        <v>1584</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -14658,7 +14864,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="70">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
@@ -14684,11 +14890,11 @@
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>10.083333333333334</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -14722,8 +14928,8 @@
         <v>30</v>
       </c>
       <c r="C12" s="59">
-        <f>72+31+1224+53+1440+864</f>
-        <v>3684</v>
+        <f>36+1224+53+1440+864</f>
+        <v>3617</v>
       </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
@@ -14743,7 +14949,7 @@
       </c>
       <c r="P12" s="66"/>
       <c r="Q12" s="66">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R12" s="67"/>
       <c r="S12" s="62"/>
@@ -14753,11 +14959,11 @@
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>89184</v>
+        <v>87744</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>3716</v>
+        <v>3656</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -14865,7 +15071,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
@@ -14889,11 +15095,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -15055,7 +15261,7 @@
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
       <c r="H17" s="70">
-        <f>24*3</f>
+        <f>3*24</f>
         <v>72</v>
       </c>
       <c r="I17" s="70"/>
@@ -15327,7 +15533,7 @@
         <v>48</v>
       </c>
       <c r="U21" s="75">
-        <f t="shared" si="4"/>
+        <f>C21*24+M21*24+O21*24+Q21*24+T21</f>
         <v>48</v>
       </c>
       <c r="V21" s="75">
@@ -15444,7 +15650,7 @@
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
       <c r="H23" s="70">
-        <f>24*37+19</f>
+        <f>37*24+19</f>
         <v>907</v>
       </c>
       <c r="I23" s="70"/>
@@ -15512,7 +15718,7 @@
         <v>56</v>
       </c>
       <c r="C24" s="70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
@@ -15539,11 +15745,11 @@
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -15586,14 +15792,14 @@
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="71">
+      <c r="I25" s="70">
         <v>1</v>
       </c>
+      <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
       <c r="M25" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" s="74"/>
       <c r="O25" s="70">
@@ -15609,11 +15815,11 @@
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>2257</v>
+        <v>2233</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>94.041666666666671</v>
+        <v>93.041666666666671</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -15633,10 +15839,7 @@
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
       <c r="G26" s="70"/>
-      <c r="H26" s="70">
-        <f>24*3</f>
-        <v>72</v>
-      </c>
+      <c r="H26" s="70"/>
       <c r="I26" s="70"/>
       <c r="J26" s="71"/>
       <c r="K26" s="72"/>
@@ -15650,15 +15853,15 @@
       <c r="S26" s="55"/>
       <c r="T26" s="58">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="U26" s="75">
         <f t="shared" si="4"/>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="V26" s="75">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -15678,9 +15881,7 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70">
-        <v>2</v>
-      </c>
+      <c r="C27" s="70"/>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -15703,11 +15904,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -15728,8 +15929,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="70">
-        <f>63+35</f>
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
@@ -15740,15 +15940,15 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73">
-        <v>2</v>
-      </c>
+      <c r="M28" s="73"/>
       <c r="N28" s="74"/>
       <c r="O28" s="70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
+      <c r="Q28" s="71">
+        <v>5</v>
+      </c>
       <c r="R28" s="72"/>
       <c r="S28" s="55"/>
       <c r="T28" s="58">
@@ -15757,11 +15957,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>2472</v>
+        <v>1608</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -15782,28 +15982,24 @@
         <v>13</v>
       </c>
       <c r="C29" s="70">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
-      <c r="H29" s="70">
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
         <v>5</v>
       </c>
-      <c r="I29" s="70"/>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
-      <c r="M29" s="73">
-        <v>2</v>
-      </c>
+      <c r="M29" s="73"/>
       <c r="N29" s="74"/>
       <c r="O29" s="70"/>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71">
-        <v>1</v>
-      </c>
+      <c r="Q29" s="71"/>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
@@ -15812,11 +16008,11 @@
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>16.208333333333332</v>
+        <v>3.2083333333333335</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -15827,9 +16023,7 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70">
-        <v>1</v>
-      </c>
+      <c r="C30" s="70"/>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -15839,7 +16033,9 @@
       <c r="J30" s="71"/>
       <c r="K30" s="72"/>
       <c r="L30" s="55"/>
-      <c r="M30" s="73"/>
+      <c r="M30" s="73">
+        <v>1</v>
+      </c>
       <c r="N30" s="74"/>
       <c r="O30" s="70"/>
       <c r="P30" s="71"/>
@@ -15905,37 +16101,38 @@
       <c r="B32" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="70"/>
+      <c r="C32" s="70">
+        <v>3</v>
+      </c>
       <c r="D32" s="70"/>
       <c r="E32" s="70"/>
       <c r="F32" s="70"/>
       <c r="G32" s="70"/>
-      <c r="H32" s="70">
-        <f>5*24</f>
-        <v>120</v>
-      </c>
+      <c r="H32" s="70"/>
       <c r="I32" s="70"/>
       <c r="J32" s="71"/>
       <c r="K32" s="72"/>
       <c r="L32" s="55"/>
       <c r="M32" s="73"/>
       <c r="N32" s="74"/>
-      <c r="O32" s="70"/>
+      <c r="O32" s="70">
+        <v>1</v>
+      </c>
       <c r="P32" s="71"/>
       <c r="Q32" s="71"/>
       <c r="R32" s="72"/>
       <c r="S32" s="55"/>
       <c r="T32" s="58">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="U32" s="75">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="V32" s="75">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
@@ -15946,15 +16143,14 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>4</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
       <c r="G33" s="70"/>
-      <c r="H33" s="70">
-        <f>5*24</f>
-        <v>120</v>
-      </c>
+      <c r="H33" s="70"/>
       <c r="I33" s="70"/>
       <c r="J33" s="71"/>
       <c r="K33" s="72"/>
@@ -15968,15 +16164,15 @@
       <c r="S33" s="55"/>
       <c r="T33" s="58">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -15988,28 +16184,28 @@
         <v>17</v>
       </c>
       <c r="C34" s="70">
-        <f>72+62</f>
-        <v>134</v>
+        <f>216+48</f>
+        <v>264</v>
       </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="71">
+      <c r="I34" s="70">
         <v>1</v>
       </c>
+      <c r="J34" s="71"/>
       <c r="K34" s="72">
         <v>1</v>
       </c>
       <c r="L34" s="55"/>
       <c r="M34" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N34" s="74"/>
       <c r="O34" s="70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P34" s="71">
         <v>12</v>
@@ -16025,11 +16221,11 @@
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>3350</v>
+        <v>6494</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>139.58333333333334</v>
+        <v>270.58333333333331</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16117,13 +16313,15 @@
         <v>19</v>
       </c>
       <c r="C37" s="59">
-        <f>24+48+756+2160</f>
-        <v>2988</v>
+        <f>2160+324+96</f>
+        <v>2580</v>
       </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
+      <c r="G37" s="59">
+        <v>648</v>
+      </c>
       <c r="H37" s="59">
         <v>3</v>
       </c>
@@ -16138,15 +16336,15 @@
       </c>
       <c r="L37" s="62"/>
       <c r="M37" s="63">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="N37" s="64"/>
       <c r="O37" s="65">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="P37" s="66"/>
       <c r="Q37" s="66">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
@@ -16155,12 +16353,12 @@
         <v>13</v>
       </c>
       <c r="U37" s="77">
-        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>18235</v>
+        <f>C37*6+G37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>20545</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>3039.1666666666665</v>
+        <v>3424.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -16172,37 +16370,38 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="70"/>
+      <c r="C38" s="70">
+        <v>1</v>
+      </c>
       <c r="D38" s="70"/>
       <c r="E38" s="70"/>
       <c r="F38" s="70"/>
       <c r="G38" s="70"/>
-      <c r="H38" s="70">
-        <f>24*3</f>
-        <v>72</v>
-      </c>
+      <c r="H38" s="70"/>
       <c r="I38" s="70"/>
       <c r="J38" s="71"/>
       <c r="K38" s="72"/>
       <c r="L38" s="55"/>
       <c r="M38" s="73"/>
       <c r="N38" s="74"/>
-      <c r="O38" s="70"/>
+      <c r="O38" s="70">
+        <v>1</v>
+      </c>
       <c r="P38" s="71"/>
       <c r="Q38" s="71"/>
       <c r="R38" s="72"/>
       <c r="S38" s="55"/>
       <c r="T38" s="75">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="U38" s="75">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="V38" s="75">
         <f>U38/24</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -16252,29 +16451,24 @@
         <v>21</v>
       </c>
       <c r="C40" s="59">
-        <f>3+4</f>
-        <v>7</v>
+        <f>126+70</f>
+        <v>196</v>
       </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
       <c r="G40" s="59"/>
-      <c r="H40" s="59">
-        <f>63*24</f>
-        <v>1512</v>
-      </c>
+      <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
       <c r="K40" s="61">
         <v>20</v>
       </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63">
-        <v>1</v>
-      </c>
+      <c r="M40" s="63"/>
       <c r="N40" s="64"/>
       <c r="O40" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P40" s="66"/>
       <c r="Q40" s="66">
@@ -16284,15 +16478,15 @@
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>1532</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>1820</v>
+        <v>4796</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>75.833333333333329</v>
+        <v>199.83333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16303,37 +16497,45 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>192+18</f>
+        <v>210</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="82">
-        <f>384*12</f>
-        <v>4608</v>
-      </c>
+      <c r="G41" s="82">
+        <v>288</v>
+      </c>
+      <c r="H41" s="82"/>
       <c r="I41" s="82"/>
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>20</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
-        <f t="shared" si="0"/>
-        <v>4608</v>
+        <f>H41+I41+J41+K41+N41+P41+R41</f>
+        <v>0</v>
       </c>
       <c r="U41" s="88">
-        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>4608</v>
+        <f>C41*12+G41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>6456</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>384</v>
+        <v>538</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16374,22 +16576,24 @@
         <v>23</v>
       </c>
       <c r="C43" s="65">
-        <f>18+24192+5400+10260+19+1296</f>
-        <v>41185</v>
+        <f>22032+8100+10260</f>
+        <v>40392</v>
       </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="G43" s="65">
+        <v>864</v>
+      </c>
       <c r="H43" s="65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I43" s="65">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J43" s="66">
-        <f>18*6+4</f>
-        <v>112</v>
+        <f>20*6+2</f>
+        <v>122</v>
       </c>
       <c r="K43" s="67">
         <f>46*6+2</f>
@@ -16397,29 +16601,29 @@
       </c>
       <c r="L43" s="62"/>
       <c r="M43" s="63">
-        <v>563</v>
+        <v>284</v>
       </c>
       <c r="N43" s="64"/>
       <c r="O43" s="65">
-        <v>402</v>
+        <v>358</v>
       </c>
       <c r="P43" s="66"/>
       <c r="Q43" s="66">
-        <v>648</v>
+        <v>483</v>
       </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="U43" s="77">
-        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>257187</v>
+        <f>C43*6+G43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>254703</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>42864.5</v>
+        <v>42450.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16464,10 +16668,7 @@
       <c r="E45" s="70"/>
       <c r="F45" s="70"/>
       <c r="G45" s="70"/>
-      <c r="H45" s="70">
-        <f>24*3</f>
-        <v>72</v>
-      </c>
+      <c r="H45" s="70"/>
       <c r="I45" s="70"/>
       <c r="J45" s="71"/>
       <c r="K45" s="72"/>
@@ -16481,15 +16682,15 @@
       <c r="S45" s="55"/>
       <c r="T45" s="75">
         <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -16500,9 +16701,7 @@
       <c r="B46" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="70">
-        <v>4</v>
-      </c>
+      <c r="C46" s="70"/>
       <c r="D46" s="70"/>
       <c r="E46" s="70"/>
       <c r="F46" s="70"/>
@@ -16525,11 +16724,11 @@
       </c>
       <c r="U46" s="75">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="V46" s="75">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16541,8 +16740,8 @@
         <v>25</v>
       </c>
       <c r="C47" s="65">
-        <f>106+648+324+98+540+432+432+106</f>
-        <v>2686</v>
+        <f>106+648+324+98+540+103+324+432+106</f>
+        <v>2681</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
@@ -16560,17 +16759,15 @@
       </c>
       <c r="L47" s="62"/>
       <c r="M47" s="63">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N47" s="64"/>
       <c r="O47" s="65">
+        <v>16</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
         <v>18</v>
-      </c>
-      <c r="P47" s="66">
-        <v>2</v>
-      </c>
-      <c r="Q47" s="66">
-        <v>20</v>
       </c>
       <c r="R47" s="67">
         <v>3</v>
@@ -16578,15 +16775,15 @@
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>16457</v>
+        <v>16341</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>2742.8333333333335</v>
+        <v>2723.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -16603,7 +16800,6 @@
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
       <c r="H48" s="70">
-        <f>24</f>
         <v>24</v>
       </c>
       <c r="I48" s="70"/>
@@ -16793,7 +16989,7 @@
         <v>63</v>
       </c>
       <c r="C53" s="70">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
@@ -16817,11 +17013,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -16947,7 +17143,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>51308</v>
+        <v>50472</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -16957,19 +17153,19 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>7769</v>
+        <v>1192</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
@@ -16977,7 +17173,7 @@
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>613</v>
+        <v>356</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -16985,15 +17181,15 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
@@ -17002,15 +17198,15 @@
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>8253</v>
+        <v>1693</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>407433</v>
+        <v>410911</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>53678.75</v>
+        <v>53864.416666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -20219,13 +20415,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -23158,13 +23354,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C171AA16-74C8-4D79-9684-F36EF775212A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558DFF91-2701-4A33-AEB4-3FCB02D649B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="14" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
@@ -20888,34 +20888,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>24</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>25.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -20950,7 +20958,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>44+43</f>
+        <v>87</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -20960,11 +20971,17 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -20973,11 +20990,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -21012,7 +21029,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>85</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -21035,11 +21054,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2040</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -21074,7 +21093,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>62</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -21097,11 +21118,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -21136,7 +21157,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>4</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -21144,7 +21167,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -21155,15 +21180,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -21196,7 +21221,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>3+1224+53+1440+864</f>
+        <v>3584</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -21206,24 +21234,34 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
+      <c r="M12" s="63">
+        <v>8</v>
+      </c>
+      <c r="N12" s="64">
+        <v>4</v>
+      </c>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>17</v>
+      </c>
       <c r="R12" s="67"/>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>86871</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3619.625</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -21265,12 +21303,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -21284,15 +21326,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -21326,7 +21368,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -21349,11 +21393,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -21514,7 +21558,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -21528,15 +21575,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -21630,12 +21677,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>1*24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -21649,15 +21701,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -21691,7 +21743,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -21714,11 +21768,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -21757,7 +21811,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -21771,15 +21828,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -21819,7 +21876,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -21832,15 +21891,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -21888,7 +21947,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -21902,15 +21964,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -21953,12 +22015,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>4</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -21972,15 +22039,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -22014,34 +22081,45 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>24+61</f>
+        <v>85</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>1</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>88.041666666666671</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -22150,7 +22228,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <v>38</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -22160,11 +22240,17 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
       <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
+      <c r="Q28" s="71">
+        <v>4</v>
+      </c>
       <c r="R28" s="72"/>
       <c r="S28" s="55"/>
       <c r="T28" s="58">
@@ -22173,11 +22259,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -22204,7 +22290,9 @@
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
       <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
@@ -22216,15 +22304,15 @@
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -22349,7 +22437,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>3</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -22372,11 +22462,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -22387,34 +22477,49 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>216+34</f>
+        <v>250</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
+      <c r="H34" s="70">
+        <v>1</v>
+      </c>
       <c r="I34" s="70"/>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
+      <c r="P34" s="71">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6158</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>256.58333333333331</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22501,34 +22606,51 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>2160+648</f>
+        <v>2808</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>6</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>30</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>73</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>117</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>18181</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3030.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -22616,7 +22738,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>65+126</f>
+        <v>191</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -22624,26 +22749,34 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>195.83333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22654,7 +22787,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>288+71</f>
+        <v>359</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -22664,11 +22800,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>12</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>48</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -22677,11 +22819,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>5148</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22721,34 +22863,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>20736+12528+10260</f>
+        <v>43524</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>3</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>25*6+4</f>
+        <v>154</v>
+      </c>
+      <c r="K43" s="67">
+        <f>46*6+2</f>
+        <v>278</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>307</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>328</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>432</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>267993</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>44665.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22864,34 +23025,51 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>106+648+324+88+540+103+324+432+106</f>
+        <v>2671</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>6</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>13</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16245</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2707.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -22907,7 +23085,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -22921,15 +23101,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -23016,7 +23196,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -23039,11 +23221,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -23092,7 +23274,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -23115,11 +23299,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -23245,7 +23429,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>53831</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -23259,56 +23443,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1190</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1738</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>416944</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>55415.041666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -26517,13 +26701,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -29456,13 +29640,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -32395,13 +32579,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558DFF91-2701-4A33-AEB4-3FCB02D649B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA6751C-3B16-4093-BA35-6EBDD84DED1E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="14" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="15" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -23791,7 +23791,7 @@
     <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
     <col min="3" max="6" width="10" style="9" customWidth="1"/>
     <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
     <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
@@ -24011,34 +24011,44 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>23</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>25.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -24073,7 +24083,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>43+43</f>
+        <v>86</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -24083,11 +24096,17 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -24096,11 +24115,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -24135,7 +24154,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>81</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -24147,9 +24168,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -24158,11 +24183,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2040</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -24197,7 +24222,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>58</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -24209,9 +24236,13 @@
       <c r="L10" s="55"/>
       <c r="M10" s="73"/>
       <c r="N10" s="74"/>
-      <c r="O10" s="70"/>
+      <c r="O10" s="70">
+        <v>2</v>
+      </c>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>2</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -24220,11 +24251,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -24259,7 +24290,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>4</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -24267,7 +24300,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -24278,15 +24313,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -24319,7 +24354,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+1368+57+864</f>
+        <v>3566</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -24331,22 +24369,28 @@
       <c r="L12" s="62"/>
       <c r="M12" s="63"/>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
+      <c r="O12" s="65">
+        <v>8</v>
+      </c>
+      <c r="P12" s="66">
+        <v>14</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>17</v>
+      </c>
       <c r="R12" s="67"/>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>86198</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3591.5833333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -24388,12 +24432,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -24407,15 +24455,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -24449,7 +24497,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -24472,11 +24522,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -24637,7 +24687,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -24651,15 +24704,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -24753,12 +24806,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -24772,15 +24830,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -24814,7 +24872,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -24837,11 +24897,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -24880,7 +24940,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -24894,15 +24957,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -24943,7 +25006,9 @@
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
       <c r="I22" s="70"/>
-      <c r="J22" s="71"/>
+      <c r="J22" s="71">
+        <v>20</v>
+      </c>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
       <c r="M22" s="73"/>
@@ -24955,15 +25020,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -25011,7 +25076,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -25025,15 +25093,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -25076,12 +25144,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>4</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -25095,15 +25168,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -25137,34 +25210,45 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>22+61</f>
+        <v>83</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2089</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>87.041666666666671</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -25236,11 +25320,17 @@
       <c r="J27" s="71"/>
       <c r="K27" s="72"/>
       <c r="L27" s="55"/>
-      <c r="M27" s="73"/>
+      <c r="M27" s="73">
+        <v>40</v>
+      </c>
       <c r="N27" s="74"/>
-      <c r="O27" s="70"/>
+      <c r="O27" s="70">
+        <v>3</v>
+      </c>
       <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
+      <c r="Q27" s="71">
+        <v>1</v>
+      </c>
       <c r="R27" s="72"/>
       <c r="S27" s="55"/>
       <c r="T27" s="58">
@@ -25249,11 +25339,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -25326,7 +25416,9 @@
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
@@ -25339,15 +25431,15 @@
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -25472,7 +25564,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>2</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -25486,7 +25580,9 @@
       <c r="N33" s="74"/>
       <c r="O33" s="70"/>
       <c r="P33" s="71"/>
-      <c r="Q33" s="71"/>
+      <c r="Q33" s="71">
+        <v>1</v>
+      </c>
       <c r="R33" s="72"/>
       <c r="S33" s="55"/>
       <c r="T33" s="58">
@@ -25495,11 +25591,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -25510,34 +25606,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>32+216</f>
+        <v>248</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
+      <c r="H34" s="70">
+        <v>1</v>
+      </c>
       <c r="I34" s="70"/>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6098</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>254.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -25624,34 +25733,51 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>1944+97+648</f>
+        <v>2689</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>6</v>
+      </c>
+      <c r="K37" s="61">
+        <v>3</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>26</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>20</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>109</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>17077</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>2846.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -25739,7 +25865,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>25+126</f>
+        <v>151</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -25747,26 +25876,34 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>3740</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>155.83333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25777,7 +25914,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>288+49</f>
+        <v>337</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -25789,9 +25929,13 @@
       <c r="L41" s="85"/>
       <c r="M41" s="86"/>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>12</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>27</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -25800,11 +25944,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>4512</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -25844,34 +25988,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>19440+14364+10260</f>
+        <v>44064</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>12</v>
+      </c>
+      <c r="I43" s="65">
+        <v>1</v>
+      </c>
+      <c r="J43" s="66">
+        <f>26*6+5</f>
+        <v>161</v>
+      </c>
+      <c r="K43" s="67">
+        <f>46*6+2</f>
+        <v>278</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>442</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>435</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>596</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>273674</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>45612.333333333336</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -25987,34 +26150,51 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>106+648+324+88+540+103+324+432+106</f>
+        <v>2671</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
       <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="I47" s="65">
+        <v>1</v>
+      </c>
+      <c r="J47" s="66">
+        <v>1</v>
+      </c>
+      <c r="K47" s="67">
+        <v>4</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>6</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>10</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16227</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2704.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -26031,7 +26211,9 @@
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
       <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
+      <c r="I48" s="70">
+        <v>24</v>
+      </c>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
       <c r="L48" s="55"/>
@@ -26044,15 +26226,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -26139,7 +26321,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -26162,11 +26346,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -26215,7 +26399,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -26238,11 +26424,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -26368,7 +26554,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>54119</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -26382,23 +26568,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1174</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -26406,32 +26592,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>774</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1730</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>419078</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>56047.333333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005F6013-B67A-42AC-B279-ABD3095BBECD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F99487C-EF5A-4961-95F8-067C72AB95F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -30281,34 +30281,44 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>23</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>25.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -30343,7 +30353,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>43+43</f>
+        <v>86</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -30353,11 +30366,17 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -30366,11 +30385,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -30405,7 +30424,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>78</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -30417,9 +30438,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>1</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -30428,11 +30453,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>1944</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -30467,7 +30492,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>54</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -30479,9 +30506,13 @@
       <c r="L10" s="55"/>
       <c r="M10" s="73"/>
       <c r="N10" s="74"/>
-      <c r="O10" s="70"/>
+      <c r="O10" s="70">
+        <v>2</v>
+      </c>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>1</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -30490,11 +30521,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -30529,7 +30560,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>4</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -30537,7 +30570,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -30548,15 +30583,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -30589,7 +30624,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+1296+864+16</f>
+        <v>3453</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -30599,24 +30637,34 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>27</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67">
+        <v>10</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>84266</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3511.0833333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -30658,12 +30706,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -30677,15 +30729,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -30719,7 +30771,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -30742,11 +30796,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -30907,7 +30961,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -30921,15 +30978,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -31023,12 +31080,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -31042,15 +31104,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -31084,7 +31146,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -31107,11 +31171,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -31150,7 +31214,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -31164,15 +31231,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -31212,7 +31279,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -31225,15 +31294,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -31281,7 +31350,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -31295,15 +31367,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -31346,12 +31418,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>4</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -31365,15 +31442,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -31407,34 +31484,45 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <f>61+20</f>
+        <v>81</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2041</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>85.041666666666671</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -31553,9 +31641,13 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
       <c r="P28" s="71"/>
       <c r="Q28" s="71"/>
       <c r="R28" s="72"/>
@@ -31566,11 +31658,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -31596,7 +31688,9 @@
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
@@ -31609,15 +31703,15 @@
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -31742,7 +31836,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>2</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -31765,11 +31861,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -31780,34 +31876,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>28+216</f>
+        <v>244</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
+      <c r="H34" s="70">
+        <v>1</v>
+      </c>
       <c r="I34" s="70"/>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
       <c r="M34" s="73"/>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>1</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5930</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>247.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -31894,34 +32001,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>36+1512+648</f>
+        <v>2196</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>1</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>29</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>21</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>91</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>14035</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>2339.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -32009,7 +32134,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>126+25</f>
+        <v>151</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -32017,26 +32145,32 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
       <c r="P40" s="66"/>
       <c r="Q40" s="66"/>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>3692</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>153.83333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -32047,7 +32181,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>96+61</f>
+        <v>157</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -32057,11 +32194,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>3</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>11</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>25</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -32070,11 +32213,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -32114,34 +32257,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>16632+18036+10260</f>
+        <v>44928</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
       <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>3*6</f>
+        <v>18</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>700</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>443</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>486</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>279800</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>46633.333333333336</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -32257,34 +32417,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>101+648+324+88+540+103+324+432+106</f>
+        <v>2666</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
       <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
+      <c r="I47" s="65">
+        <v>1</v>
+      </c>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>11</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>10</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16227</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2704.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -32300,7 +32475,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -32314,15 +32491,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -32409,7 +32586,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -32432,11 +32611,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -32485,7 +32664,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>6</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -32495,7 +32676,9 @@
       <c r="J53" s="71"/>
       <c r="K53" s="72"/>
       <c r="L53" s="55"/>
-      <c r="M53" s="73"/>
+      <c r="M53" s="73">
+        <v>1</v>
+      </c>
       <c r="N53" s="74"/>
       <c r="O53" s="70"/>
       <c r="P53" s="71"/>
@@ -32508,11 +32691,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -32638,7 +32821,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>54178</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -32652,23 +32835,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1186</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -32676,32 +32859,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1748</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>416582</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>56238.833333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -32971,13 +33154,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -41985,13 +42168,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -44924,13 +45107,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -47863,13 +48046,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F99487C-EF5A-4961-95F8-067C72AB95F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB28054-B115-4A60-9C37-FC6ED9222E7B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -31,8 +31,8 @@
     <sheet name="07-24-2026" sheetId="71" r:id="rId16"/>
     <sheet name="07-26-2026" sheetId="73" r:id="rId17"/>
     <sheet name="07-27-2026" sheetId="74" r:id="rId18"/>
-    <sheet name="07-28-2026" sheetId="72" r:id="rId19"/>
-    <sheet name="07-29-2026" sheetId="75" r:id="rId20"/>
+    <sheet name="07-29-2026" sheetId="75" r:id="rId19"/>
+    <sheet name="07-28-2026" sheetId="72" r:id="rId20"/>
     <sheet name="07-30-2026" sheetId="76" r:id="rId21"/>
     <sheet name="07-31-2026" sheetId="77" r:id="rId22"/>
   </sheets>
@@ -54,8 +54,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="15">'07-24-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'07-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'07-27-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="18">'07-28-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="19">'07-29-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'07-28-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'07-29-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'07-30-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'07-31-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
@@ -33172,7 +33172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24BAC45D-8114-4367-9C64-0D4E3AF47D3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E39F8B-9D9D-45B9-8256-B550131C2C86}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -33229,7 +33229,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -33320,8 +33320,8 @@
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
-      <c r="P5" s="105"/>
-      <c r="Q5" s="105"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
       <c r="T5" s="119"/>
@@ -33360,13 +33360,13 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="105"/>
+      <c r="J6" s="106"/>
       <c r="K6" s="38"/>
       <c r="M6" s="37"/>
       <c r="N6" s="49"/>
       <c r="O6" s="40"/>
-      <c r="P6" s="105"/>
-      <c r="Q6" s="105"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="106"/>
       <c r="R6" s="38"/>
       <c r="S6" s="9"/>
       <c r="T6" s="39"/>
@@ -33403,34 +33403,44 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>23</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>25.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -33465,7 +33475,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>43+43</f>
+        <v>86</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -33475,11 +33488,17 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
       <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
@@ -33488,11 +33507,11 @@
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -33527,7 +33546,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>78</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -33539,9 +33560,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>1</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -33550,11 +33575,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>1944</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -33589,7 +33614,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>54</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -33601,9 +33628,13 @@
       <c r="L10" s="55"/>
       <c r="M10" s="73"/>
       <c r="N10" s="74"/>
-      <c r="O10" s="70"/>
+      <c r="O10" s="70">
+        <v>1</v>
+      </c>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>1</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -33612,11 +33643,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1344</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -33651,7 +33682,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>4</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -33659,7 +33692,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -33670,15 +33705,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -33711,7 +33746,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+864+1296+1</f>
+        <v>3438</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -33721,24 +33759,32 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>4</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="O12" s="65">
+        <v>8</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="Q12" s="66">
+        <v>18</v>
+      </c>
+      <c r="R12" s="67">
+        <v>4</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>83236</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3468.1666666666665</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -33780,12 +33826,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -33799,15 +33849,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -33841,7 +33891,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -33864,11 +33916,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -34029,7 +34081,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -34043,15 +34098,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -34145,12 +34200,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -34164,15 +34224,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -34206,7 +34266,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -34229,11 +34291,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -34272,7 +34334,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -34286,15 +34351,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -34334,7 +34399,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -34347,15 +34414,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -34403,7 +34470,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -34417,15 +34487,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -34468,12 +34538,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -34482,20 +34557,22 @@
       <c r="N24" s="74"/>
       <c r="O24" s="70"/>
       <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
+      <c r="Q24" s="71">
+        <v>2</v>
+      </c>
       <c r="R24" s="72"/>
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -34529,34 +34606,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>61</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>21</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2041</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>85.041666666666671</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -34675,9 +34762,13 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
       <c r="P28" s="71"/>
       <c r="Q28" s="71"/>
       <c r="R28" s="72"/>
@@ -34688,11 +34779,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -34719,7 +34810,9 @@
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
       <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
@@ -34731,15 +34824,15 @@
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -34864,7 +34957,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>2</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -34887,11 +34982,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -34902,34 +34997,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>216+8</f>
+        <v>224</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>20</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>1</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5930</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>247.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -35016,34 +35124,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>648+90+1296</f>
+        <v>2034</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>1</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>181</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>14</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>61</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>13753</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>2292.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -35131,7 +35257,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>126+25</f>
+        <v>151</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -35139,26 +35268,32 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
       <c r="P40" s="66"/>
       <c r="Q40" s="66"/>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>3692</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>153.83333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -35169,7 +35304,9 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <v>57</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -35179,11 +35316,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>53</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>40</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -35192,11 +35335,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>1920</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -35236,34 +35379,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>15680+18036+10260</f>
+        <v>43976</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
+      <c r="H43" s="65">
+        <v>12</v>
+      </c>
+      <c r="I43" s="65">
+        <f>3*6</f>
+        <v>18</v>
+      </c>
+      <c r="J43" s="66">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="K43" s="67"/>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>269</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>430</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>564</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>271892</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>45315.333333333336</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -35379,34 +35539,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>101+648+324+88+540+103+324+432+106</f>
+        <v>2666</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>11</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>10</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16227</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2704.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -35422,7 +35597,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -35436,15 +35613,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -35531,7 +35708,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -35554,11 +35733,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -35607,7 +35786,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>6</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -35621,7 +35802,9 @@
       <c r="N53" s="74"/>
       <c r="O53" s="70"/>
       <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
+      <c r="Q53" s="71">
+        <v>1</v>
+      </c>
       <c r="R53" s="72"/>
       <c r="S53" s="55"/>
       <c r="T53" s="75">
@@ -35630,11 +35813,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -35760,7 +35943,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>52907</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -35774,23 +35957,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1198</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -35798,7 +35981,7 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
@@ -35806,24 +35989,24 @@
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>704</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1726</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>406882</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>54792.916666666672</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -39247,7 +39430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E39F8B-9D9D-45B9-8256-B550131C2C86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24BAC45D-8114-4367-9C64-0D4E3AF47D3C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -39304,7 +39487,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -39395,8 +39578,8 @@
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
-      <c r="P5" s="106"/>
-      <c r="Q5" s="106"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
       <c r="T5" s="119"/>
@@ -39435,13 +39618,13 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="106"/>
+      <c r="J6" s="105"/>
       <c r="K6" s="38"/>
       <c r="M6" s="37"/>
       <c r="N6" s="49"/>
       <c r="O6" s="40"/>
-      <c r="P6" s="106"/>
-      <c r="Q6" s="106"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
       <c r="R6" s="38"/>
       <c r="S6" s="9"/>
       <c r="T6" s="39"/>
@@ -39478,7 +39661,9 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>25</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
@@ -39501,11 +39686,11 @@
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -41835,7 +42020,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -41894,11 +42079,11 @@
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/INVENTORY COUNT SHEET - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB28054-B115-4A60-9C37-FC6ED9222E7B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6070977D-B4A2-40B9-91BF-5E8117A6204E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -32,9 +32,8 @@
     <sheet name="07-26-2026" sheetId="73" r:id="rId17"/>
     <sheet name="07-27-2026" sheetId="74" r:id="rId18"/>
     <sheet name="07-29-2026" sheetId="75" r:id="rId19"/>
-    <sheet name="07-28-2026" sheetId="72" r:id="rId20"/>
-    <sheet name="07-30-2026" sheetId="76" r:id="rId21"/>
-    <sheet name="07-31-2026" sheetId="77" r:id="rId22"/>
+    <sheet name="07-30-2026" sheetId="76" r:id="rId20"/>
+    <sheet name="07-31-2026" sheetId="77" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'07-02-2026'!$A$1:$W$59</definedName>
@@ -54,10 +53,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="15">'07-24-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'07-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'07-27-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="19">'07-28-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'07-29-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="20">'07-30-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="21">'07-31-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'07-30-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'07-31-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -76,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="90">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -338,9 +336,6 @@
   </si>
   <si>
     <t>DATE: 07/27/2026</t>
-  </si>
-  <si>
-    <t>DATE: 07/28/2026</t>
   </si>
   <si>
     <t>DATE: 07/29/2026</t>
@@ -33229,7 +33224,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -39430,2947 +39425,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24BAC45D-8114-4367-9C64-0D4E3AF47D3C}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:BB81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
-    <col min="3" max="6" width="10" style="9" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
-    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="10" style="9" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="9" customWidth="1"/>
-    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="10" style="9" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
-    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
-    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
-    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
-    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
-    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="55" max="16384" width="9.140625" style="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="114" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-    </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="B2" s="28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="115" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
-      <c r="M4" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="O4" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q4" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
-        <v>68</v>
-      </c>
-      <c r="U4" s="124" t="s">
-        <v>67</v>
-      </c>
-      <c r="V4" s="107" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
-      <c r="AH4" s="11"/>
-      <c r="AI4" s="11"/>
-      <c r="AJ4" s="11"/>
-      <c r="AK4" s="11"/>
-      <c r="AL4" s="11"/>
-      <c r="AM4" s="11"/>
-      <c r="AN4" s="11"/>
-      <c r="AO4" s="11"/>
-      <c r="AP4" s="11"/>
-      <c r="AQ4" s="11"/>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="11"/>
-      <c r="AT4" s="11"/>
-      <c r="AU4" s="11"/>
-      <c r="AV4" s="11"/>
-      <c r="AW4" s="11"/>
-      <c r="AX4" s="11"/>
-      <c r="AY4" s="11"/>
-      <c r="AZ4" s="11"/>
-      <c r="BA4" s="11"/>
-      <c r="BB4" s="11"/>
-    </row>
-    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="37"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="J5" s="122" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="123"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="105"/>
-      <c r="Q5" s="105"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
-      <c r="AF5" s="11"/>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="11"/>
-      <c r="AJ5" s="11"/>
-      <c r="AK5" s="11"/>
-      <c r="AL5" s="11"/>
-      <c r="AM5" s="11"/>
-      <c r="AN5" s="11"/>
-      <c r="AO5" s="11"/>
-      <c r="AP5" s="11"/>
-      <c r="AQ5" s="11"/>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="11"/>
-      <c r="AT5" s="11"/>
-      <c r="AU5" s="11"/>
-      <c r="AV5" s="11"/>
-      <c r="AW5" s="11"/>
-      <c r="AX5" s="11"/>
-      <c r="AY5" s="11"/>
-      <c r="AZ5" s="11"/>
-      <c r="BA5" s="11"/>
-      <c r="BB5" s="11"/>
-    </row>
-    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="37"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="105"/>
-      <c r="Q6" s="105"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="39"/>
-      <c r="AF6" s="11"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="11"/>
-      <c r="AJ6" s="11"/>
-      <c r="AK6" s="11"/>
-      <c r="AL6" s="11"/>
-      <c r="AM6" s="11"/>
-      <c r="AN6" s="11"/>
-      <c r="AO6" s="11"/>
-      <c r="AP6" s="11"/>
-      <c r="AQ6" s="11"/>
-      <c r="AR6" s="11"/>
-      <c r="AS6" s="11"/>
-      <c r="AT6" s="11"/>
-      <c r="AU6" s="11"/>
-      <c r="AV6" s="11"/>
-      <c r="AW6" s="11"/>
-      <c r="AX6" s="11"/>
-      <c r="AY6" s="11"/>
-      <c r="AZ6" s="11"/>
-      <c r="BA6" s="11"/>
-      <c r="BB6" s="11"/>
-    </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
-        <v>1</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="52">
-        <v>25</v>
-      </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="58">
-        <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
-      </c>
-      <c r="U7" s="58">
-        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>600</v>
-      </c>
-      <c r="V7" s="58">
-        <f>U7/24</f>
-        <v>25</v>
-      </c>
-      <c r="W7" s="50"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="12"/>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="12"/>
-      <c r="AQ7" s="12"/>
-      <c r="AR7" s="12"/>
-      <c r="AS7" s="12"/>
-      <c r="AT7" s="12"/>
-      <c r="AU7" s="12"/>
-      <c r="AV7" s="12"/>
-      <c r="AW7" s="12"/>
-      <c r="AX7" s="12"/>
-      <c r="AY7" s="12"/>
-      <c r="AZ7" s="12"/>
-      <c r="BA7" s="12"/>
-      <c r="BB7" s="12"/>
-    </row>
-    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27">
-        <f>A7+1</f>
-        <v>2</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="62"/>
-      <c r="T8" s="68">
-        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="69">
-        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="69">
-        <f>U8/24</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="50"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="12"/>
-      <c r="AM8" s="12"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="12"/>
-      <c r="AQ8" s="12"/>
-      <c r="AR8" s="12"/>
-      <c r="AS8" s="12"/>
-      <c r="AT8" s="12"/>
-      <c r="AU8" s="12"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="12"/>
-      <c r="AX8" s="12"/>
-      <c r="AY8" s="12"/>
-      <c r="AZ8" s="12"/>
-      <c r="BA8" s="12"/>
-      <c r="BB8" s="12"/>
-    </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
-        <f t="shared" ref="A9:A57" si="1">A8+1</f>
-        <v>3</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U9" s="76">
-        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
-      </c>
-      <c r="V9" s="76">
-        <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="50"/>
-      <c r="AF9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AH9" s="12"/>
-      <c r="AI9" s="12"/>
-      <c r="AJ9" s="12"/>
-      <c r="AK9" s="12"/>
-      <c r="AL9" s="12"/>
-      <c r="AM9" s="12"/>
-      <c r="AN9" s="12"/>
-      <c r="AO9" s="12"/>
-      <c r="AP9" s="12"/>
-      <c r="AQ9" s="12"/>
-      <c r="AR9" s="12"/>
-      <c r="AS9" s="12"/>
-      <c r="AT9" s="12"/>
-      <c r="AU9" s="12"/>
-      <c r="AV9" s="12"/>
-      <c r="AW9" s="12"/>
-      <c r="AX9" s="12"/>
-      <c r="AY9" s="12"/>
-      <c r="AZ9" s="12"/>
-      <c r="BA9" s="12"/>
-      <c r="BB9" s="12"/>
-    </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="73"/>
-      <c r="N10" s="74"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="50"/>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="12"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="12"/>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="12"/>
-      <c r="AS10" s="12"/>
-      <c r="AT10" s="12"/>
-      <c r="AU10" s="12"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="12"/>
-      <c r="AX10" s="12"/>
-      <c r="AY10" s="12"/>
-      <c r="AZ10" s="12"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="12"/>
-    </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="73"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="12"/>
-      <c r="AI11" s="12"/>
-      <c r="AJ11" s="12"/>
-      <c r="AK11" s="12"/>
-      <c r="AL11" s="12"/>
-      <c r="AM11" s="12"/>
-      <c r="AN11" s="12"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="12"/>
-      <c r="AQ11" s="12"/>
-      <c r="AR11" s="12"/>
-      <c r="AS11" s="12"/>
-      <c r="AT11" s="12"/>
-      <c r="AU11" s="12"/>
-      <c r="AV11" s="12"/>
-      <c r="AW11" s="12"/>
-      <c r="AX11" s="12"/>
-      <c r="AY11" s="12"/>
-      <c r="AZ11" s="12"/>
-      <c r="BA11" s="12"/>
-      <c r="BB11" s="12"/>
-    </row>
-    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27">
-        <v>7</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
-      <c r="S12" s="62"/>
-      <c r="T12" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="69">
-        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="69">
-        <f>U12/24</f>
-        <v>0</v>
-      </c>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="12"/>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="12"/>
-      <c r="AK12" s="12"/>
-      <c r="AL12" s="12"/>
-      <c r="AM12" s="12"/>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="12"/>
-      <c r="AP12" s="12"/>
-      <c r="AQ12" s="12"/>
-      <c r="AR12" s="12"/>
-      <c r="AS12" s="12"/>
-      <c r="AT12" s="12"/>
-      <c r="AU12" s="12"/>
-      <c r="AV12" s="12"/>
-      <c r="AW12" s="12"/>
-      <c r="AX12" s="12"/>
-      <c r="AY12" s="12"/>
-      <c r="AZ12" s="12"/>
-      <c r="BA12" s="12"/>
-      <c r="BB12" s="12"/>
-    </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A13" s="27">
-        <v>11</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="73"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="76">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="76">
-        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="76">
-        <f>U13/24</f>
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12"/>
-      <c r="AG13" s="12"/>
-      <c r="AH13" s="12"/>
-      <c r="AI13" s="12"/>
-      <c r="AJ13" s="12"/>
-      <c r="AK13" s="12"/>
-      <c r="AL13" s="12"/>
-      <c r="AM13" s="12"/>
-      <c r="AN13" s="12"/>
-      <c r="AO13" s="12"/>
-      <c r="AP13" s="12"/>
-      <c r="AQ13" s="12"/>
-      <c r="AR13" s="12"/>
-      <c r="AS13" s="12"/>
-      <c r="AT13" s="12"/>
-      <c r="AU13" s="12"/>
-      <c r="AV13" s="12"/>
-      <c r="AW13" s="12"/>
-      <c r="AX13" s="12"/>
-      <c r="AY13" s="12"/>
-      <c r="AZ13" s="12"/>
-      <c r="BA13" s="12"/>
-      <c r="BB13" s="12"/>
-    </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="75">
-        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
-      </c>
-      <c r="V14" s="75">
-        <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
-      </c>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="12"/>
-      <c r="AK14" s="12"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="12"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="12"/>
-      <c r="AQ14" s="12"/>
-      <c r="AR14" s="12"/>
-      <c r="AS14" s="12"/>
-      <c r="AT14" s="12"/>
-      <c r="AU14" s="12"/>
-      <c r="AV14" s="12"/>
-      <c r="AW14" s="12"/>
-      <c r="AX14" s="12"/>
-      <c r="AY14" s="12"/>
-      <c r="AZ14" s="12"/>
-      <c r="BA14" s="12"/>
-      <c r="BB14" s="12"/>
-    </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="73"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF15" s="12"/>
-      <c r="AG15" s="12"/>
-      <c r="AH15" s="12"/>
-      <c r="AI15" s="12"/>
-      <c r="AJ15" s="12"/>
-      <c r="AK15" s="12"/>
-      <c r="AL15" s="12"/>
-      <c r="AM15" s="12"/>
-      <c r="AN15" s="12"/>
-      <c r="AO15" s="12"/>
-      <c r="AP15" s="12"/>
-      <c r="AQ15" s="12"/>
-      <c r="AR15" s="12"/>
-      <c r="AS15" s="12"/>
-      <c r="AT15" s="12"/>
-      <c r="AU15" s="12"/>
-      <c r="AV15" s="12"/>
-      <c r="AW15" s="12"/>
-      <c r="AX15" s="12"/>
-      <c r="AY15" s="12"/>
-      <c r="AZ15" s="12"/>
-      <c r="BA15" s="12"/>
-      <c r="BB15" s="12"/>
-    </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A16" s="27">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="73"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF16" s="12"/>
-      <c r="AG16" s="12"/>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="12"/>
-      <c r="AJ16" s="12"/>
-      <c r="AK16" s="12"/>
-      <c r="AL16" s="12"/>
-      <c r="AM16" s="12"/>
-      <c r="AN16" s="12"/>
-      <c r="AO16" s="12"/>
-      <c r="AP16" s="12"/>
-      <c r="AQ16" s="12"/>
-      <c r="AR16" s="12"/>
-      <c r="AS16" s="12"/>
-      <c r="AT16" s="12"/>
-      <c r="AU16" s="12"/>
-      <c r="AV16" s="12"/>
-      <c r="AW16" s="12"/>
-      <c r="AX16" s="12"/>
-      <c r="AY16" s="12"/>
-      <c r="AZ16" s="12"/>
-      <c r="BA16" s="12"/>
-      <c r="BB16" s="12"/>
-    </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A17" s="27">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="73"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-      <c r="AS17" s="12"/>
-      <c r="AT17" s="12"/>
-      <c r="AU17" s="12"/>
-      <c r="AV17" s="12"/>
-      <c r="AW17" s="12"/>
-      <c r="AX17" s="12"/>
-      <c r="AY17" s="12"/>
-      <c r="AZ17" s="12"/>
-      <c r="BA17" s="12"/>
-      <c r="BB17" s="12"/>
-    </row>
-    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="73"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF18" s="12"/>
-      <c r="AG18" s="12"/>
-      <c r="AH18" s="12"/>
-      <c r="AI18" s="12"/>
-      <c r="AJ18" s="12"/>
-      <c r="AK18" s="12"/>
-      <c r="AL18" s="12"/>
-      <c r="AM18" s="12"/>
-      <c r="AN18" s="12"/>
-      <c r="AO18" s="12"/>
-      <c r="AP18" s="12"/>
-      <c r="AQ18" s="12"/>
-      <c r="AR18" s="12"/>
-      <c r="AS18" s="12"/>
-      <c r="AT18" s="12"/>
-      <c r="AU18" s="12"/>
-      <c r="AV18" s="12"/>
-      <c r="AW18" s="12"/>
-      <c r="AX18" s="12"/>
-      <c r="AY18" s="12"/>
-      <c r="AZ18" s="12"/>
-      <c r="BA18" s="12"/>
-      <c r="BB18" s="12"/>
-    </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A19" s="27">
-        <v>16</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="73"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF19" s="12"/>
-      <c r="AG19" s="12"/>
-      <c r="AH19" s="12"/>
-      <c r="AI19" s="12"/>
-      <c r="AJ19" s="12"/>
-      <c r="AK19" s="12"/>
-      <c r="AL19" s="12"/>
-      <c r="AM19" s="12"/>
-      <c r="AN19" s="12"/>
-      <c r="AO19" s="12"/>
-      <c r="AP19" s="12"/>
-      <c r="AQ19" s="12"/>
-      <c r="AR19" s="12"/>
-      <c r="AS19" s="12"/>
-      <c r="AT19" s="12"/>
-      <c r="AU19" s="12"/>
-      <c r="AV19" s="12"/>
-      <c r="AW19" s="12"/>
-      <c r="AX19" s="12"/>
-      <c r="AY19" s="12"/>
-      <c r="AZ19" s="12"/>
-      <c r="BA19" s="12"/>
-      <c r="BB19" s="12"/>
-    </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A20" s="27">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="73"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF20" s="12"/>
-      <c r="AG20" s="12"/>
-      <c r="AH20" s="12"/>
-      <c r="AI20" s="12"/>
-      <c r="AJ20" s="12"/>
-      <c r="AK20" s="12"/>
-      <c r="AL20" s="12"/>
-      <c r="AM20" s="12"/>
-      <c r="AN20" s="12"/>
-      <c r="AO20" s="12"/>
-      <c r="AP20" s="12"/>
-      <c r="AQ20" s="12"/>
-      <c r="AR20" s="12"/>
-      <c r="AS20" s="12"/>
-      <c r="AT20" s="12"/>
-      <c r="AU20" s="12"/>
-      <c r="AV20" s="12"/>
-      <c r="AW20" s="12"/>
-      <c r="AX20" s="12"/>
-      <c r="AY20" s="12"/>
-      <c r="AZ20" s="12"/>
-      <c r="BA20" s="12"/>
-      <c r="BB20" s="12"/>
-    </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A21" s="27">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="73"/>
-      <c r="N21" s="74"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF21" s="12"/>
-      <c r="AG21" s="12"/>
-      <c r="AH21" s="12"/>
-      <c r="AI21" s="12"/>
-      <c r="AJ21" s="12"/>
-      <c r="AK21" s="12"/>
-      <c r="AL21" s="12"/>
-      <c r="AM21" s="12"/>
-      <c r="AN21" s="12"/>
-      <c r="AO21" s="12"/>
-      <c r="AP21" s="12"/>
-      <c r="AQ21" s="12"/>
-      <c r="AR21" s="12"/>
-      <c r="AS21" s="12"/>
-      <c r="AT21" s="12"/>
-      <c r="AU21" s="12"/>
-      <c r="AV21" s="12"/>
-      <c r="AW21" s="12"/>
-      <c r="AX21" s="12"/>
-      <c r="AY21" s="12"/>
-      <c r="AZ21" s="12"/>
-      <c r="BA21" s="12"/>
-      <c r="BB21" s="12"/>
-    </row>
-    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="12"/>
-      <c r="AG22" s="12"/>
-      <c r="AH22" s="12"/>
-      <c r="AI22" s="12"/>
-      <c r="AJ22" s="12"/>
-      <c r="AK22" s="12"/>
-      <c r="AL22" s="12"/>
-      <c r="AM22" s="12"/>
-      <c r="AN22" s="12"/>
-      <c r="AO22" s="12"/>
-      <c r="AP22" s="12"/>
-      <c r="AQ22" s="12"/>
-      <c r="AR22" s="12"/>
-      <c r="AS22" s="12"/>
-      <c r="AT22" s="12"/>
-      <c r="AU22" s="12"/>
-      <c r="AV22" s="12"/>
-      <c r="AW22" s="12"/>
-      <c r="AX22" s="12"/>
-      <c r="AY22" s="12"/>
-      <c r="AZ22" s="12"/>
-      <c r="BA22" s="12"/>
-      <c r="BB22" s="12"/>
-    </row>
-    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="74"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="9"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="12"/>
-      <c r="AG23" s="12"/>
-      <c r="AH23" s="12"/>
-      <c r="AI23" s="12"/>
-      <c r="AJ23" s="12"/>
-      <c r="AK23" s="12"/>
-      <c r="AL23" s="12"/>
-      <c r="AM23" s="12"/>
-      <c r="AN23" s="12"/>
-      <c r="AO23" s="12"/>
-      <c r="AP23" s="12"/>
-      <c r="AQ23" s="12"/>
-      <c r="AR23" s="12"/>
-      <c r="AS23" s="12"/>
-      <c r="AT23" s="12"/>
-      <c r="AU23" s="12"/>
-      <c r="AV23" s="12"/>
-      <c r="AW23" s="12"/>
-      <c r="AX23" s="12"/>
-      <c r="AY23" s="12"/>
-      <c r="AZ23" s="12"/>
-      <c r="BA23" s="12"/>
-      <c r="BB23" s="12"/>
-    </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="55"/>
-      <c r="T24" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="12"/>
-      <c r="AG24" s="12"/>
-      <c r="AH24" s="12"/>
-      <c r="AI24" s="12"/>
-      <c r="AJ24" s="12"/>
-      <c r="AK24" s="12"/>
-      <c r="AL24" s="12"/>
-      <c r="AM24" s="12"/>
-      <c r="AN24" s="12"/>
-      <c r="AO24" s="12"/>
-      <c r="AP24" s="12"/>
-      <c r="AQ24" s="12"/>
-      <c r="AR24" s="12"/>
-      <c r="AS24" s="12"/>
-      <c r="AT24" s="12"/>
-      <c r="AU24" s="12"/>
-      <c r="AV24" s="12"/>
-      <c r="AW24" s="12"/>
-      <c r="AX24" s="12"/>
-      <c r="AY24" s="12"/>
-      <c r="AZ24" s="12"/>
-      <c r="BA24" s="12"/>
-      <c r="BB24" s="12"/>
-    </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AY25" s="14" t="e">
-        <f>#REF!-AY24</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="73"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="71"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="55"/>
-      <c r="T26" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="9"/>
-      <c r="AE26" s="9"/>
-    </row>
-    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="27">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="73"/>
-      <c r="N27" s="74"/>
-      <c r="O27" s="70"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="55"/>
-      <c r="T27" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="9"/>
-      <c r="AE27" s="9"/>
-    </row>
-    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="55"/>
-      <c r="T28" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="9"/>
-      <c r="AE28" s="9"/>
-    </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="73"/>
-      <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="55"/>
-      <c r="T29" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V29" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V30" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="55"/>
-      <c r="T31" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V31" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="74"/>
-      <c r="O32" s="70"/>
-      <c r="P32" s="71"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="55"/>
-      <c r="T32" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V32" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="27">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="72"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="73"/>
-      <c r="N33" s="74"/>
-      <c r="O33" s="70"/>
-      <c r="P33" s="71"/>
-      <c r="Q33" s="71"/>
-      <c r="R33" s="72"/>
-      <c r="S33" s="55"/>
-      <c r="T33" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V33" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="27">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
-      <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="72"/>
-      <c r="S34" s="55"/>
-      <c r="T34" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U34" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V34" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="72"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="73"/>
-      <c r="N35" s="74"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="71"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="72"/>
-      <c r="S35" s="55"/>
-      <c r="T35" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U35" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V35" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="27">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="73"/>
-      <c r="N36" s="74"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="71"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="55"/>
-      <c r="T36" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U36" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V36" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="27">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="B37" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
-      <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
-      <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
-      <c r="R37" s="67"/>
-      <c r="S37" s="62"/>
-      <c r="T37" s="77">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="77">
-        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="77">
-        <f>U37/6</f>
-        <v>0</v>
-      </c>
-      <c r="W37" s="50"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="27">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="72"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="73"/>
-      <c r="N38" s="74"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="71"/>
-      <c r="Q38" s="71"/>
-      <c r="R38" s="72"/>
-      <c r="S38" s="55"/>
-      <c r="T38" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U38" s="75">
-        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
-      </c>
-      <c r="V38" s="75">
-        <f>U38/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="27">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="B39" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
-      <c r="E39" s="78"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="78"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="80"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="73"/>
-      <c r="N39" s="74"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="71"/>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="72"/>
-      <c r="S39" s="95"/>
-      <c r="T39" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U39" s="75">
-        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="75">
-        <f>U39/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="27">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="B40" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
-      <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
-      <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="62"/>
-      <c r="T40" s="77">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U40" s="77">
-        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="77">
-        <f>U40/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="27">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="B41" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="82"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
-      <c r="I41" s="82"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
-      <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
-      <c r="R41" s="84"/>
-      <c r="S41" s="85"/>
-      <c r="T41" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U41" s="88">
-        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="88">
-        <f>U41/12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="27">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="B42" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="71"/>
-      <c r="K42" s="72"/>
-      <c r="L42" s="55"/>
-      <c r="M42" s="73"/>
-      <c r="N42" s="74"/>
-      <c r="O42" s="70"/>
-      <c r="P42" s="71"/>
-      <c r="Q42" s="71"/>
-      <c r="R42" s="72"/>
-      <c r="S42" s="55"/>
-      <c r="T42" s="75"/>
-      <c r="U42" s="75"/>
-      <c r="V42" s="75"/>
-    </row>
-    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="27">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="B43" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="65"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
-      <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
-      <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
-      <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
-      <c r="R43" s="67"/>
-      <c r="S43" s="62"/>
-      <c r="T43" s="77">
-        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
-      </c>
-      <c r="U43" s="77">
-        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
-      </c>
-      <c r="V43" s="77">
-        <f>U43/6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="27">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="70"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="71"/>
-      <c r="K44" s="72"/>
-      <c r="L44" s="55"/>
-      <c r="M44" s="73"/>
-      <c r="N44" s="74"/>
-      <c r="O44" s="70"/>
-      <c r="P44" s="71"/>
-      <c r="Q44" s="71"/>
-      <c r="R44" s="72"/>
-      <c r="S44" s="55"/>
-      <c r="T44" s="75"/>
-      <c r="U44" s="75"/>
-      <c r="V44" s="75"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A45" s="27">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
-      <c r="I45" s="70"/>
-      <c r="J45" s="71"/>
-      <c r="K45" s="72"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="73"/>
-      <c r="N45" s="74"/>
-      <c r="O45" s="70"/>
-      <c r="P45" s="71"/>
-      <c r="Q45" s="71"/>
-      <c r="R45" s="72"/>
-      <c r="S45" s="55"/>
-      <c r="T45" s="75">
-        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
-        <v>0</v>
-      </c>
-      <c r="U45" s="75">
-        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
-      </c>
-      <c r="V45" s="75">
-        <f>U45/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="27">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="71"/>
-      <c r="K46" s="72"/>
-      <c r="L46" s="55"/>
-      <c r="M46" s="73"/>
-      <c r="N46" s="74"/>
-      <c r="O46" s="70"/>
-      <c r="P46" s="71"/>
-      <c r="Q46" s="71"/>
-      <c r="R46" s="72"/>
-      <c r="S46" s="55"/>
-      <c r="T46" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U46" s="75">
-        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="75">
-        <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="27">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-      <c r="B47" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="65"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
-      <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
-      <c r="S47" s="62"/>
-      <c r="T47" s="77">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U47" s="77">
-        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="77">
-        <f>U47/6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="27">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="71"/>
-      <c r="K48" s="72"/>
-      <c r="L48" s="55"/>
-      <c r="M48" s="73"/>
-      <c r="N48" s="74"/>
-      <c r="O48" s="70"/>
-      <c r="P48" s="71"/>
-      <c r="Q48" s="71"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="55"/>
-      <c r="T48" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U48" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V48" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="27">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-      <c r="B49" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="70"/>
-      <c r="I49" s="70"/>
-      <c r="J49" s="71"/>
-      <c r="K49" s="72"/>
-      <c r="L49" s="55"/>
-      <c r="M49" s="73"/>
-      <c r="N49" s="74"/>
-      <c r="O49" s="70"/>
-      <c r="P49" s="71"/>
-      <c r="Q49" s="71"/>
-      <c r="R49" s="72"/>
-      <c r="S49" s="55"/>
-      <c r="T49" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U49" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V49" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="27">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="70"/>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="71"/>
-      <c r="K50" s="72"/>
-      <c r="L50" s="55"/>
-      <c r="M50" s="73"/>
-      <c r="N50" s="74"/>
-      <c r="O50" s="70"/>
-      <c r="P50" s="71"/>
-      <c r="Q50" s="71"/>
-      <c r="R50" s="72"/>
-      <c r="S50" s="55"/>
-      <c r="T50" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U50" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V50" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="27">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="B51" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="65"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="65"/>
-      <c r="I51" s="65"/>
-      <c r="J51" s="66"/>
-      <c r="K51" s="67"/>
-      <c r="L51" s="62"/>
-      <c r="M51" s="63"/>
-      <c r="N51" s="64"/>
-      <c r="O51" s="65"/>
-      <c r="P51" s="66"/>
-      <c r="Q51" s="66"/>
-      <c r="R51" s="67"/>
-      <c r="S51" s="62"/>
-      <c r="T51" s="77">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U51" s="77">
-        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
-      </c>
-      <c r="V51" s="77">
-        <f>U51/6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="27">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" s="70"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="71"/>
-      <c r="K52" s="72"/>
-      <c r="L52" s="55"/>
-      <c r="M52" s="73"/>
-      <c r="N52" s="74"/>
-      <c r="O52" s="70"/>
-      <c r="P52" s="71"/>
-      <c r="Q52" s="71"/>
-      <c r="R52" s="72"/>
-      <c r="S52" s="55"/>
-      <c r="T52" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U52" s="75">
-        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
-        <v>0</v>
-      </c>
-      <c r="V52" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="27">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" s="70"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="71"/>
-      <c r="K53" s="72"/>
-      <c r="L53" s="55"/>
-      <c r="M53" s="73"/>
-      <c r="N53" s="74"/>
-      <c r="O53" s="70"/>
-      <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
-      <c r="R53" s="72"/>
-      <c r="S53" s="55"/>
-      <c r="T53" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U53" s="75">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V53" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A54" s="27">
-        <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="71"/>
-      <c r="K54" s="72"/>
-      <c r="L54" s="55"/>
-      <c r="M54" s="73"/>
-      <c r="N54" s="74"/>
-      <c r="O54" s="70"/>
-      <c r="P54" s="71"/>
-      <c r="Q54" s="71"/>
-      <c r="R54" s="72"/>
-      <c r="S54" s="55"/>
-      <c r="T54" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U54" s="75">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V54" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A55" s="27">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="71"/>
-      <c r="K55" s="72"/>
-      <c r="L55" s="55"/>
-      <c r="M55" s="73"/>
-      <c r="N55" s="74"/>
-      <c r="O55" s="70"/>
-      <c r="P55" s="71"/>
-      <c r="Q55" s="71"/>
-      <c r="R55" s="72"/>
-      <c r="S55" s="55"/>
-      <c r="T55" s="75"/>
-      <c r="U55" s="75"/>
-      <c r="V55" s="75"/>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A56" s="27">
-        <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="70"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="71"/>
-      <c r="K56" s="72"/>
-      <c r="L56" s="55"/>
-      <c r="M56" s="73"/>
-      <c r="N56" s="74"/>
-      <c r="O56" s="70"/>
-      <c r="P56" s="71"/>
-      <c r="Q56" s="71"/>
-      <c r="R56" s="72"/>
-      <c r="S56" s="55"/>
-      <c r="T56" s="75"/>
-      <c r="U56" s="75"/>
-      <c r="V56" s="75"/>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A57" s="27">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-      <c r="B57" s="26"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="70"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="71"/>
-      <c r="K57" s="72"/>
-      <c r="L57" s="55"/>
-      <c r="M57" s="73"/>
-      <c r="N57" s="74"/>
-      <c r="O57" s="70"/>
-      <c r="P57" s="71"/>
-      <c r="Q57" s="71"/>
-      <c r="R57" s="72"/>
-      <c r="S57" s="55"/>
-      <c r="T57" s="75"/>
-      <c r="U57" s="75"/>
-      <c r="V57" s="75"/>
-    </row>
-    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C58" s="2">
-        <f>SUM(C7:C57)</f>
-        <v>25</v>
-      </c>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2">
-        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="5">
-        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
-      </c>
-      <c r="N58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="55"/>
-      <c r="T58" s="4">
-        <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="90">
-        <f>SUM(U7:U57)</f>
-        <v>600</v>
-      </c>
-      <c r="V58" s="4">
-        <f>SUM(V7:V57)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="111" t="s">
-        <v>41</v>
-      </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
-      <c r="U60" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B61" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="20"/>
-      <c r="U61" s="7"/>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B62" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="44"/>
-      <c r="K62" s="21"/>
-      <c r="U62" s="3"/>
-    </row>
-    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="23"/>
-      <c r="U63" s="8"/>
-    </row>
-    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B65" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="45"/>
-      <c r="K65" s="20"/>
-      <c r="U65" s="7"/>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B66" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="44"/>
-      <c r="K66" s="21"/>
-      <c r="U66" s="3"/>
-    </row>
-    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="23"/>
-      <c r="U67" s="8"/>
-    </row>
-    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B69" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="45"/>
-      <c r="K69" s="20"/>
-      <c r="U69" s="7"/>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B70" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="44"/>
-      <c r="K70" s="21"/>
-      <c r="U70" s="3"/>
-    </row>
-    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="23"/>
-      <c r="U71" s="8"/>
-    </row>
-    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B73" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="45"/>
-      <c r="K73" s="20"/>
-      <c r="U73" s="7"/>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B74" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="44"/>
-      <c r="K74" s="21"/>
-      <c r="U74" s="3"/>
-    </row>
-    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="23"/>
-      <c r="U75" s="8"/>
-    </row>
-    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B77" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="45"/>
-      <c r="K77" s="20"/>
-      <c r="U77" s="7"/>
-    </row>
-    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B78" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="44"/>
-      <c r="K78" s="21"/>
-      <c r="U78" s="3"/>
-    </row>
-    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
-      <c r="G79" s="22"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="23"/>
-      <c r="U79" s="8"/>
-    </row>
-    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="47"/>
-      <c r="K81" s="18"/>
-      <c r="U81" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C60:K60"/>
-    <mergeCell ref="I1:U1"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="24" max="80" man="1"/>
-  </colBreaks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF7CD35C-82A7-4B10-91F4-B10E138A0401}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -42428,7 +39482,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -42602,34 +39656,47 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>22</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
+      <c r="G7" s="52">
+        <f>24*10</f>
+        <v>240</v>
+      </c>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>2</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
-        <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <f>G7+H7+I7+J7+K7+N7+P7+R7</f>
+        <v>249</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>35.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -42664,7 +39731,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>43+43</f>
+        <v>86</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -42674,24 +39744,30 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
       <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2148</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -42726,11 +39802,16 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <v>78</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
+      <c r="G9" s="70">
+        <f>24*30</f>
+        <v>720</v>
+      </c>
       <c r="H9" s="70"/>
       <c r="I9" s="70"/>
       <c r="J9" s="71"/>
@@ -42738,22 +39819,26 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>1</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>G9+H9+I9+J9+K9+N9+P9+R9</f>
+        <v>720</v>
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2664</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -42788,11 +39873,16 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <v>54</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
+      <c r="G10" s="70">
+        <f>24*10</f>
+        <v>240</v>
+      </c>
       <c r="H10" s="70"/>
       <c r="I10" s="70"/>
       <c r="J10" s="71"/>
@@ -42800,22 +39890,26 @@
       <c r="L10" s="55"/>
       <c r="M10" s="73"/>
       <c r="N10" s="74"/>
-      <c r="O10" s="70"/>
+      <c r="O10" s="70">
+        <v>1</v>
+      </c>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>1</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>G10+H10+I10+J10+K10+N10+P10+R10</f>
+        <v>240</v>
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -42850,15 +39944,22 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>4</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
+      <c r="G11" s="70">
+        <f>24*5</f>
+        <v>120</v>
+      </c>
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -42868,16 +39969,16 @@
       <c r="R11" s="72"/>
       <c r="S11" s="55"/>
       <c r="T11" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>G11+H11+I11+J11+K11+N11+P11+R11</f>
+        <v>122</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -42910,7 +40011,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+864+1224+18+245</f>
+        <v>3628</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -42920,24 +40024,34 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>4</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="O12" s="65">
+        <v>12</v>
+      </c>
+      <c r="P12" s="66">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>15</v>
+      </c>
+      <c r="R12" s="67">
+        <v>3</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>87840</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3660</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -42979,12 +40093,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -42998,15 +40116,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -43040,7 +40158,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -43063,11 +40183,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -43228,7 +40348,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -43242,15 +40365,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -43344,12 +40467,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -43363,15 +40491,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -43405,7 +40533,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -43428,11 +40558,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -43471,7 +40601,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -43485,15 +40618,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -43533,7 +40666,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -43546,15 +40681,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -43602,7 +40737,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -43616,15 +40754,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -43667,12 +40805,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -43681,20 +40824,22 @@
       <c r="N24" s="74"/>
       <c r="O24" s="70"/>
       <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
+      <c r="Q24" s="71">
+        <v>2</v>
+      </c>
       <c r="R24" s="72"/>
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -43728,34 +40873,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>56</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>2</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>1</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -43864,7 +41019,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <v>30</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -43874,9 +41031,13 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>1</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
       <c r="P28" s="71"/>
       <c r="Q28" s="71"/>
       <c r="R28" s="72"/>
@@ -43887,11 +41048,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -43918,7 +41079,9 @@
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
       <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
@@ -43930,15 +41093,15 @@
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -44063,7 +41226,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>2</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -44086,11 +41251,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -44101,34 +41266,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>216+6</f>
+        <v>222</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
       <c r="M34" s="73"/>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>1</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5402</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>225.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -44215,34 +41391,55 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>648+1296+68</f>
+        <v>2012</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="G37" s="59">
+        <f>1404*6</f>
+        <v>8424</v>
+      </c>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>1</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>19</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>20</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>51</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>G37+H37+I37+J37+K37+N37+P37+R37</f>
+        <v>8437</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>21049</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3508.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -44330,7 +41527,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>23+63+63</f>
+        <v>149</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -44338,26 +41538,34 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>1</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>3668</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>152.83333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -44368,7 +41576,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>96+57</f>
+        <v>153</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -44378,11 +41589,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>3</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>30</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -44391,11 +41608,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -44435,34 +41652,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>648+14256+18900+10260</f>
+        <v>44064</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
       <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>3*6</f>
+        <v>18</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>389</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>445</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>360</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>272006</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>45334.333333333336</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -44578,34 +41812,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>101+648+324+88+540+103+324+432+106</f>
+        <v>2666</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
       <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
+      <c r="I47" s="65">
+        <v>1</v>
+      </c>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>11</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>10</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16227</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2704.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -44622,7 +41871,9 @@
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
       <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
+      <c r="I48" s="70">
+        <v>24</v>
+      </c>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
       <c r="L48" s="55"/>
@@ -44635,15 +41886,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -44730,7 +41981,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -44753,11 +42006,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -44806,7 +42059,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>6</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -44820,7 +42075,9 @@
       <c r="N53" s="74"/>
       <c r="O53" s="70"/>
       <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
+      <c r="Q53" s="71">
+        <v>1</v>
+      </c>
       <c r="R53" s="72"/>
       <c r="S53" s="55"/>
       <c r="T53" s="75">
@@ -44829,11 +42086,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -44959,7 +42216,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>53279</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -44969,27 +42226,27 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9744</v>
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1161</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -44997,32 +42254,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>11502</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>420228</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>56293.25</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -45309,7 +42566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3713548B-2701-43CA-8542-BB44D58CA025}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -45367,7 +42624,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -45541,34 +42798,45 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <f>10+22</f>
+        <v>32</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>2</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>35.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -45603,7 +42871,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>43+43</f>
+        <v>86</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -45616,21 +42887,25 @@
       <c r="M8" s="63"/>
       <c r="N8" s="64"/>
       <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -45665,7 +42940,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>63+30</f>
+        <v>93</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -45677,9 +42955,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>2</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>15</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -45688,11 +42970,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2640</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -45727,7 +43009,10 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <f>39+10</f>
+        <v>49</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -45739,9 +43024,13 @@
       <c r="L10" s="55"/>
       <c r="M10" s="73"/>
       <c r="N10" s="74"/>
-      <c r="O10" s="70"/>
+      <c r="O10" s="70">
+        <v>2</v>
+      </c>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>15</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -45750,11 +43039,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -45789,7 +43078,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -45797,7 +43088,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -45808,15 +43101,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -45849,7 +43142,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>216+29+1224+53+1224+864</f>
+        <v>3610</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -45859,24 +43155,32 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>9</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="Q12" s="66">
+        <v>14</v>
+      </c>
+      <c r="R12" s="67">
+        <v>10</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>87442</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3643.4166666666665</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -45918,12 +43222,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -45937,15 +43245,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -45979,7 +43287,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -46002,11 +43312,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -46167,7 +43477,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -46181,15 +43494,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -46283,12 +43596,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -46302,15 +43620,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -46344,7 +43662,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -46367,11 +43687,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -46410,7 +43730,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -46424,15 +43747,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -46472,7 +43795,9 @@
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -46485,15 +43810,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -46541,7 +43866,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -46555,15 +43883,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -46606,12 +43934,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -46620,20 +43953,22 @@
       <c r="N24" s="74"/>
       <c r="O24" s="70"/>
       <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
+      <c r="Q24" s="71">
+        <v>2</v>
+      </c>
       <c r="R24" s="72"/>
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -46667,34 +44002,42 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>56</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>2</v>
+      </c>
       <c r="P25" s="71"/>
       <c r="Q25" s="71"/>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1417</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>59.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -46803,7 +44146,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <v>18</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -46813,9 +44158,13 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>13</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
       <c r="P28" s="71"/>
       <c r="Q28" s="71"/>
       <c r="R28" s="72"/>
@@ -46826,11 +44175,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -46857,7 +44206,9 @@
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
       <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
@@ -46869,15 +44220,15 @@
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -47002,7 +44353,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>2</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -47025,11 +44378,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -47040,34 +44393,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>144+67</f>
+        <v>211</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>11</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
       <c r="Q34" s="71"/>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5378</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>224.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -47154,34 +44518,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>1188+74+2052</f>
+        <v>3314</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>1</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>39</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>20</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>73</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>20689</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3448.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -47269,7 +44651,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>23+63+58</f>
+        <v>144</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -47277,9 +44662,13 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>5</v>
+      </c>
       <c r="N40" s="64"/>
       <c r="O40" s="65"/>
       <c r="P40" s="66"/>
@@ -47288,15 +44677,15 @@
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>3596</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>149.83333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -47307,7 +44696,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>49+96</f>
+        <v>145</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -47317,11 +44709,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>8</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>9</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>18</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -47330,11 +44728,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -47374,34 +44772,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>13392+19548+10260</f>
+        <v>43200</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
       <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>5*6</f>
+        <v>30</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>364</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>396</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>455</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>266960</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>44493.333333333336</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -47517,34 +44932,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>101+648+324+88+540+103+324+432+106</f>
+        <v>2666</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
       <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
+      <c r="I47" s="65">
+        <v>1</v>
+      </c>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>9</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>10</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2702.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -47561,7 +44991,9 @@
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
       <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
+      <c r="I48" s="70">
+        <v>24</v>
+      </c>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
       <c r="L48" s="55"/>
@@ -47574,15 +45006,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -47669,7 +45101,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -47692,11 +45126,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -47745,7 +45179,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>6</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -47759,7 +45195,9 @@
       <c r="N53" s="74"/>
       <c r="O53" s="70"/>
       <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
+      <c r="Q53" s="71">
+        <v>1</v>
+      </c>
       <c r="R53" s="72"/>
       <c r="S53" s="55"/>
       <c r="T53" s="75">
@@ -47768,11 +45206,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -47898,7 +45336,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>53688</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -47912,23 +45350,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1161</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -47936,32 +45374,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1756</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>414052</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>55350.666666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
